--- a/display/Sim_per_Segment_v3.xlsx
+++ b/display/Sim_per_Segment_v3.xlsx
@@ -568,7 +568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X209"/>
+  <dimension ref="A1:X247"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -11076,6 +11076,1910 @@
         <v/>
       </c>
     </row>
+    <row r="212">
+      <c r="B212" s="2" t="inlineStr">
+        <is>
+          <t>◆ SPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="C213" s="3" t="inlineStr">
+        <is>
+          <t>◄ CURRENT (actuals: data + calc) ►</t>
+        </is>
+      </c>
+      <c r="D213" s="3" t="n"/>
+      <c r="E213" s="3" t="n"/>
+      <c r="F213" s="3" t="n"/>
+      <c r="G213" s="3" t="n"/>
+      <c r="I213" s="4" t="inlineStr">
+        <is>
+          <t>◄ SIMULATED (EcoGainsSim v4) ►</t>
+        </is>
+      </c>
+      <c r="J213" s="4" t="n"/>
+      <c r="K213" s="4" t="n"/>
+      <c r="L213" s="4" t="n"/>
+      <c r="M213" s="4" t="n"/>
+      <c r="O213" s="5" t="inlineStr">
+        <is>
+          <t>Δ</t>
+        </is>
+      </c>
+      <c r="P213" s="5" t="n"/>
+      <c r="Q213" s="5" t="n"/>
+      <c r="R213" s="5" t="n"/>
+      <c r="S213" s="5" t="n"/>
+      <c r="U213" s="6" t="inlineStr">
+        <is>
+          <t>◄ NET / earner (spend held constant) ►</t>
+        </is>
+      </c>
+      <c r="V213" s="6" t="n"/>
+      <c r="W213" s="6" t="n"/>
+      <c r="X213" s="6" t="n"/>
+    </row>
+    <row r="214">
+      <c r="B214" s="7" t="inlineStr">
+        <is>
+          <t>Segment</t>
+        </is>
+      </c>
+      <c r="C214" s="8" t="inlineStr">
+        <is>
+          <t>PAID</t>
+        </is>
+      </c>
+      <c r="D214" s="8" t="inlineStr">
+        <is>
+          <t>ADS</t>
+        </is>
+      </c>
+      <c r="E214" s="8" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="F214" s="8" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="G214" s="8" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="I214" s="9" t="inlineStr">
+        <is>
+          <t>PAID</t>
+        </is>
+      </c>
+      <c r="J214" s="9" t="inlineStr">
+        <is>
+          <t>ADS</t>
+        </is>
+      </c>
+      <c r="K214" s="9" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="L214" s="9" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="M214" s="9" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="O214" s="10" t="inlineStr">
+        <is>
+          <t>PAID</t>
+        </is>
+      </c>
+      <c r="P214" s="10" t="inlineStr">
+        <is>
+          <t>ADS</t>
+        </is>
+      </c>
+      <c r="Q214" s="10" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="R214" s="10" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="S214" s="10" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="U214" s="11" t="inlineStr">
+        <is>
+          <t>cur spend</t>
+        </is>
+      </c>
+      <c r="V214" s="11" t="inlineStr">
+        <is>
+          <t>cur net</t>
+        </is>
+      </c>
+      <c r="W214" s="11" t="inlineStr">
+        <is>
+          <t>new net</t>
+        </is>
+      </c>
+      <c r="X214" s="11" t="inlineStr">
+        <is>
+          <t>net Δ</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="B215" s="12" t="inlineStr">
+        <is>
+          <t>NONPAYER</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="B216" s="13" t="inlineStr">
+        <is>
+          <t>0-9</t>
+        </is>
+      </c>
+      <c r="C216" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D216" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E216" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F216" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G216" s="14">
+        <f>SUM(C216:F216)</f>
+        <v/>
+      </c>
+      <c r="I216" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J216" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K216" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L216" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M216" s="14">
+        <f>SUM(I216:L216)</f>
+        <v/>
+      </c>
+      <c r="O216" s="15">
+        <f>IFERROR(I216/C216-1,"")</f>
+        <v/>
+      </c>
+      <c r="P216" s="15">
+        <f>IFERROR(J216/D216-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q216" s="15">
+        <f>IFERROR(K216/E216-1,"")</f>
+        <v/>
+      </c>
+      <c r="R216" s="15">
+        <f>IFERROR(L216/F216-1,"")</f>
+        <v/>
+      </c>
+      <c r="S216" s="15">
+        <f>IFERROR(M216/G216-1,"")</f>
+        <v/>
+      </c>
+      <c r="U216" s="16" t="n"/>
+      <c r="V216" s="16" t="n"/>
+      <c r="W216" s="16" t="n"/>
+      <c r="X216" s="16">
+        <f>IFERROR(W216-V216,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="217">
+      <c r="B217" s="13" t="inlineStr">
+        <is>
+          <t>10-19</t>
+        </is>
+      </c>
+      <c r="C217" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D217" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E217" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F217" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G217" s="14">
+        <f>SUM(C217:F217)</f>
+        <v/>
+      </c>
+      <c r="I217" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J217" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K217" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L217" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M217" s="14">
+        <f>SUM(I217:L217)</f>
+        <v/>
+      </c>
+      <c r="O217" s="15">
+        <f>IFERROR(I217/C217-1,"")</f>
+        <v/>
+      </c>
+      <c r="P217" s="15">
+        <f>IFERROR(J217/D217-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q217" s="15">
+        <f>IFERROR(K217/E217-1,"")</f>
+        <v/>
+      </c>
+      <c r="R217" s="15">
+        <f>IFERROR(L217/F217-1,"")</f>
+        <v/>
+      </c>
+      <c r="S217" s="15">
+        <f>IFERROR(M217/G217-1,"")</f>
+        <v/>
+      </c>
+      <c r="U217" s="16" t="n"/>
+      <c r="V217" s="16" t="n"/>
+      <c r="W217" s="16" t="n"/>
+      <c r="X217" s="16">
+        <f>IFERROR(W217-V217,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="218">
+      <c r="B218" s="13" t="inlineStr">
+        <is>
+          <t>20-39</t>
+        </is>
+      </c>
+      <c r="C218" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D218" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E218" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F218" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G218" s="14">
+        <f>SUM(C218:F218)</f>
+        <v/>
+      </c>
+      <c r="I218" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J218" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K218" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L218" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M218" s="14">
+        <f>SUM(I218:L218)</f>
+        <v/>
+      </c>
+      <c r="O218" s="15">
+        <f>IFERROR(I218/C218-1,"")</f>
+        <v/>
+      </c>
+      <c r="P218" s="15">
+        <f>IFERROR(J218/D218-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q218" s="15">
+        <f>IFERROR(K218/E218-1,"")</f>
+        <v/>
+      </c>
+      <c r="R218" s="15">
+        <f>IFERROR(L218/F218-1,"")</f>
+        <v/>
+      </c>
+      <c r="S218" s="15">
+        <f>IFERROR(M218/G218-1,"")</f>
+        <v/>
+      </c>
+      <c r="U218" s="16" t="n"/>
+      <c r="V218" s="16" t="n"/>
+      <c r="W218" s="16" t="n"/>
+      <c r="X218" s="16">
+        <f>IFERROR(W218-V218,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="219">
+      <c r="B219" s="13" t="inlineStr">
+        <is>
+          <t>40-99</t>
+        </is>
+      </c>
+      <c r="C219" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D219" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E219" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F219" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G219" s="14">
+        <f>SUM(C219:F219)</f>
+        <v/>
+      </c>
+      <c r="I219" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J219" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K219" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L219" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M219" s="14">
+        <f>SUM(I219:L219)</f>
+        <v/>
+      </c>
+      <c r="O219" s="15">
+        <f>IFERROR(I219/C219-1,"")</f>
+        <v/>
+      </c>
+      <c r="P219" s="15">
+        <f>IFERROR(J219/D219-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q219" s="15">
+        <f>IFERROR(K219/E219-1,"")</f>
+        <v/>
+      </c>
+      <c r="R219" s="15">
+        <f>IFERROR(L219/F219-1,"")</f>
+        <v/>
+      </c>
+      <c r="S219" s="15">
+        <f>IFERROR(M219/G219-1,"")</f>
+        <v/>
+      </c>
+      <c r="U219" s="16" t="n"/>
+      <c r="V219" s="16" t="n"/>
+      <c r="W219" s="16" t="n"/>
+      <c r="X219" s="16">
+        <f>IFERROR(W219-V219,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="220">
+      <c r="B220" s="13" t="inlineStr">
+        <is>
+          <t>100+</t>
+        </is>
+      </c>
+      <c r="C220" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D220" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E220" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F220" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G220" s="14">
+        <f>SUM(C220:F220)</f>
+        <v/>
+      </c>
+      <c r="I220" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J220" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K220" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L220" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M220" s="14">
+        <f>SUM(I220:L220)</f>
+        <v/>
+      </c>
+      <c r="O220" s="15">
+        <f>IFERROR(I220/C220-1,"")</f>
+        <v/>
+      </c>
+      <c r="P220" s="15">
+        <f>IFERROR(J220/D220-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q220" s="15">
+        <f>IFERROR(K220/E220-1,"")</f>
+        <v/>
+      </c>
+      <c r="R220" s="15">
+        <f>IFERROR(L220/F220-1,"")</f>
+        <v/>
+      </c>
+      <c r="S220" s="15">
+        <f>IFERROR(M220/G220-1,"")</f>
+        <v/>
+      </c>
+      <c r="U220" s="16" t="n"/>
+      <c r="V220" s="16" t="n"/>
+      <c r="W220" s="16" t="n"/>
+      <c r="X220" s="16">
+        <f>IFERROR(W220-V220,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="221">
+      <c r="B221" s="17" t="inlineStr">
+        <is>
+          <t>overall</t>
+        </is>
+      </c>
+      <c r="C221" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D221" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E221" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F221" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G221" s="18">
+        <f>SUM(C221:F221)</f>
+        <v/>
+      </c>
+      <c r="I221" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J221" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K221" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L221" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M221" s="18">
+        <f>SUM(I221:L221)</f>
+        <v/>
+      </c>
+      <c r="O221" s="19">
+        <f>IFERROR(I221/C221-1,"")</f>
+        <v/>
+      </c>
+      <c r="P221" s="19">
+        <f>IFERROR(J221/D221-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q221" s="19">
+        <f>IFERROR(K221/E221-1,"")</f>
+        <v/>
+      </c>
+      <c r="R221" s="19">
+        <f>IFERROR(L221/F221-1,"")</f>
+        <v/>
+      </c>
+      <c r="S221" s="19">
+        <f>IFERROR(M221/G221-1,"")</f>
+        <v/>
+      </c>
+      <c r="U221" s="20" t="n"/>
+      <c r="V221" s="20" t="n"/>
+      <c r="W221" s="20" t="n"/>
+      <c r="X221" s="20">
+        <f>IFERROR(W221-V221,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="222">
+      <c r="B222" s="12" t="inlineStr">
+        <is>
+          <t>PAYER</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="B223" s="13" t="inlineStr">
+        <is>
+          <t>0-9</t>
+        </is>
+      </c>
+      <c r="C223" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D223" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E223" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F223" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G223" s="14">
+        <f>SUM(C223:F223)</f>
+        <v/>
+      </c>
+      <c r="I223" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J223" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K223" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L223" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M223" s="14">
+        <f>SUM(I223:L223)</f>
+        <v/>
+      </c>
+      <c r="O223" s="15">
+        <f>IFERROR(I223/C223-1,"")</f>
+        <v/>
+      </c>
+      <c r="P223" s="15">
+        <f>IFERROR(J223/D223-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q223" s="15">
+        <f>IFERROR(K223/E223-1,"")</f>
+        <v/>
+      </c>
+      <c r="R223" s="15">
+        <f>IFERROR(L223/F223-1,"")</f>
+        <v/>
+      </c>
+      <c r="S223" s="15">
+        <f>IFERROR(M223/G223-1,"")</f>
+        <v/>
+      </c>
+      <c r="U223" s="16" t="n"/>
+      <c r="V223" s="16" t="n"/>
+      <c r="W223" s="16" t="n"/>
+      <c r="X223" s="16">
+        <f>IFERROR(W223-V223,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="224">
+      <c r="B224" s="13" t="inlineStr">
+        <is>
+          <t>10-19</t>
+        </is>
+      </c>
+      <c r="C224" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D224" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E224" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F224" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G224" s="14">
+        <f>SUM(C224:F224)</f>
+        <v/>
+      </c>
+      <c r="I224" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J224" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K224" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L224" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M224" s="14">
+        <f>SUM(I224:L224)</f>
+        <v/>
+      </c>
+      <c r="O224" s="15">
+        <f>IFERROR(I224/C224-1,"")</f>
+        <v/>
+      </c>
+      <c r="P224" s="15">
+        <f>IFERROR(J224/D224-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q224" s="15">
+        <f>IFERROR(K224/E224-1,"")</f>
+        <v/>
+      </c>
+      <c r="R224" s="15">
+        <f>IFERROR(L224/F224-1,"")</f>
+        <v/>
+      </c>
+      <c r="S224" s="15">
+        <f>IFERROR(M224/G224-1,"")</f>
+        <v/>
+      </c>
+      <c r="U224" s="16" t="n"/>
+      <c r="V224" s="16" t="n"/>
+      <c r="W224" s="16" t="n"/>
+      <c r="X224" s="16">
+        <f>IFERROR(W224-V224,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="225">
+      <c r="B225" s="13" t="inlineStr">
+        <is>
+          <t>20-39</t>
+        </is>
+      </c>
+      <c r="C225" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D225" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E225" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F225" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G225" s="14">
+        <f>SUM(C225:F225)</f>
+        <v/>
+      </c>
+      <c r="I225" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J225" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K225" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L225" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M225" s="14">
+        <f>SUM(I225:L225)</f>
+        <v/>
+      </c>
+      <c r="O225" s="15">
+        <f>IFERROR(I225/C225-1,"")</f>
+        <v/>
+      </c>
+      <c r="P225" s="15">
+        <f>IFERROR(J225/D225-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q225" s="15">
+        <f>IFERROR(K225/E225-1,"")</f>
+        <v/>
+      </c>
+      <c r="R225" s="15">
+        <f>IFERROR(L225/F225-1,"")</f>
+        <v/>
+      </c>
+      <c r="S225" s="15">
+        <f>IFERROR(M225/G225-1,"")</f>
+        <v/>
+      </c>
+      <c r="U225" s="16" t="n"/>
+      <c r="V225" s="16" t="n"/>
+      <c r="W225" s="16" t="n"/>
+      <c r="X225" s="16">
+        <f>IFERROR(W225-V225,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="226">
+      <c r="B226" s="13" t="inlineStr">
+        <is>
+          <t>40-99</t>
+        </is>
+      </c>
+      <c r="C226" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D226" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E226" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F226" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G226" s="14">
+        <f>SUM(C226:F226)</f>
+        <v/>
+      </c>
+      <c r="I226" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J226" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K226" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L226" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M226" s="14">
+        <f>SUM(I226:L226)</f>
+        <v/>
+      </c>
+      <c r="O226" s="15">
+        <f>IFERROR(I226/C226-1,"")</f>
+        <v/>
+      </c>
+      <c r="P226" s="15">
+        <f>IFERROR(J226/D226-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q226" s="15">
+        <f>IFERROR(K226/E226-1,"")</f>
+        <v/>
+      </c>
+      <c r="R226" s="15">
+        <f>IFERROR(L226/F226-1,"")</f>
+        <v/>
+      </c>
+      <c r="S226" s="15">
+        <f>IFERROR(M226/G226-1,"")</f>
+        <v/>
+      </c>
+      <c r="U226" s="16" t="n"/>
+      <c r="V226" s="16" t="n"/>
+      <c r="W226" s="16" t="n"/>
+      <c r="X226" s="16">
+        <f>IFERROR(W226-V226,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="227">
+      <c r="B227" s="13" t="inlineStr">
+        <is>
+          <t>100+</t>
+        </is>
+      </c>
+      <c r="C227" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D227" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E227" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F227" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G227" s="14">
+        <f>SUM(C227:F227)</f>
+        <v/>
+      </c>
+      <c r="I227" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J227" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K227" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L227" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M227" s="14">
+        <f>SUM(I227:L227)</f>
+        <v/>
+      </c>
+      <c r="O227" s="15">
+        <f>IFERROR(I227/C227-1,"")</f>
+        <v/>
+      </c>
+      <c r="P227" s="15">
+        <f>IFERROR(J227/D227-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q227" s="15">
+        <f>IFERROR(K227/E227-1,"")</f>
+        <v/>
+      </c>
+      <c r="R227" s="15">
+        <f>IFERROR(L227/F227-1,"")</f>
+        <v/>
+      </c>
+      <c r="S227" s="15">
+        <f>IFERROR(M227/G227-1,"")</f>
+        <v/>
+      </c>
+      <c r="U227" s="16" t="n"/>
+      <c r="V227" s="16" t="n"/>
+      <c r="W227" s="16" t="n"/>
+      <c r="X227" s="16">
+        <f>IFERROR(W227-V227,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="228">
+      <c r="B228" s="17" t="inlineStr">
+        <is>
+          <t>overall</t>
+        </is>
+      </c>
+      <c r="C228" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D228" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E228" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F228" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G228" s="18">
+        <f>SUM(C228:F228)</f>
+        <v/>
+      </c>
+      <c r="I228" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J228" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K228" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L228" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M228" s="18">
+        <f>SUM(I228:L228)</f>
+        <v/>
+      </c>
+      <c r="O228" s="19">
+        <f>IFERROR(I228/C228-1,"")</f>
+        <v/>
+      </c>
+      <c r="P228" s="19">
+        <f>IFERROR(J228/D228-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q228" s="19">
+        <f>IFERROR(K228/E228-1,"")</f>
+        <v/>
+      </c>
+      <c r="R228" s="19">
+        <f>IFERROR(L228/F228-1,"")</f>
+        <v/>
+      </c>
+      <c r="S228" s="19">
+        <f>IFERROR(M228/G228-1,"")</f>
+        <v/>
+      </c>
+      <c r="U228" s="20" t="n"/>
+      <c r="V228" s="20" t="n"/>
+      <c r="W228" s="20" t="n"/>
+      <c r="X228" s="20">
+        <f>IFERROR(W228-V228,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="231">
+      <c r="B231" s="2" t="inlineStr">
+        <is>
+          <t>◆ SPTx2</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="C232" s="3" t="inlineStr">
+        <is>
+          <t>◄ CURRENT (actuals: data + calc) ►</t>
+        </is>
+      </c>
+      <c r="D232" s="3" t="n"/>
+      <c r="E232" s="3" t="n"/>
+      <c r="F232" s="3" t="n"/>
+      <c r="G232" s="3" t="n"/>
+      <c r="I232" s="4" t="inlineStr">
+        <is>
+          <t>◄ SIMULATED (EcoGainsSim v4) ►</t>
+        </is>
+      </c>
+      <c r="J232" s="4" t="n"/>
+      <c r="K232" s="4" t="n"/>
+      <c r="L232" s="4" t="n"/>
+      <c r="M232" s="4" t="n"/>
+      <c r="O232" s="5" t="inlineStr">
+        <is>
+          <t>Δ</t>
+        </is>
+      </c>
+      <c r="P232" s="5" t="n"/>
+      <c r="Q232" s="5" t="n"/>
+      <c r="R232" s="5" t="n"/>
+      <c r="S232" s="5" t="n"/>
+      <c r="U232" s="6" t="inlineStr">
+        <is>
+          <t>◄ NET / earner (spend held constant) ►</t>
+        </is>
+      </c>
+      <c r="V232" s="6" t="n"/>
+      <c r="W232" s="6" t="n"/>
+      <c r="X232" s="6" t="n"/>
+    </row>
+    <row r="233">
+      <c r="B233" s="7" t="inlineStr">
+        <is>
+          <t>Segment</t>
+        </is>
+      </c>
+      <c r="C233" s="8" t="inlineStr">
+        <is>
+          <t>PAID</t>
+        </is>
+      </c>
+      <c r="D233" s="8" t="inlineStr">
+        <is>
+          <t>ADS</t>
+        </is>
+      </c>
+      <c r="E233" s="8" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="F233" s="8" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="G233" s="8" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="I233" s="9" t="inlineStr">
+        <is>
+          <t>PAID</t>
+        </is>
+      </c>
+      <c r="J233" s="9" t="inlineStr">
+        <is>
+          <t>ADS</t>
+        </is>
+      </c>
+      <c r="K233" s="9" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="L233" s="9" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="M233" s="9" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="O233" s="10" t="inlineStr">
+        <is>
+          <t>PAID</t>
+        </is>
+      </c>
+      <c r="P233" s="10" t="inlineStr">
+        <is>
+          <t>ADS</t>
+        </is>
+      </c>
+      <c r="Q233" s="10" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="R233" s="10" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="S233" s="10" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="U233" s="11" t="inlineStr">
+        <is>
+          <t>cur spend</t>
+        </is>
+      </c>
+      <c r="V233" s="11" t="inlineStr">
+        <is>
+          <t>cur net</t>
+        </is>
+      </c>
+      <c r="W233" s="11" t="inlineStr">
+        <is>
+          <t>new net</t>
+        </is>
+      </c>
+      <c r="X233" s="11" t="inlineStr">
+        <is>
+          <t>net Δ</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="B234" s="12" t="inlineStr">
+        <is>
+          <t>NONPAYER</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="B235" s="13" t="inlineStr">
+        <is>
+          <t>0-9</t>
+        </is>
+      </c>
+      <c r="C235" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D235" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E235" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F235" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G235" s="14">
+        <f>SUM(C235:F235)</f>
+        <v/>
+      </c>
+      <c r="I235" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J235" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K235" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L235" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M235" s="14">
+        <f>SUM(I235:L235)</f>
+        <v/>
+      </c>
+      <c r="O235" s="15">
+        <f>IFERROR(I235/C235-1,"")</f>
+        <v/>
+      </c>
+      <c r="P235" s="15">
+        <f>IFERROR(J235/D235-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q235" s="15">
+        <f>IFERROR(K235/E235-1,"")</f>
+        <v/>
+      </c>
+      <c r="R235" s="15">
+        <f>IFERROR(L235/F235-1,"")</f>
+        <v/>
+      </c>
+      <c r="S235" s="15">
+        <f>IFERROR(M235/G235-1,"")</f>
+        <v/>
+      </c>
+      <c r="U235" s="16" t="n"/>
+      <c r="V235" s="16" t="n"/>
+      <c r="W235" s="16" t="n"/>
+      <c r="X235" s="16">
+        <f>IFERROR(W235-V235,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="236">
+      <c r="B236" s="13" t="inlineStr">
+        <is>
+          <t>10-19</t>
+        </is>
+      </c>
+      <c r="C236" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D236" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E236" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F236" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G236" s="14">
+        <f>SUM(C236:F236)</f>
+        <v/>
+      </c>
+      <c r="I236" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J236" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K236" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L236" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M236" s="14">
+        <f>SUM(I236:L236)</f>
+        <v/>
+      </c>
+      <c r="O236" s="15">
+        <f>IFERROR(I236/C236-1,"")</f>
+        <v/>
+      </c>
+      <c r="P236" s="15">
+        <f>IFERROR(J236/D236-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q236" s="15">
+        <f>IFERROR(K236/E236-1,"")</f>
+        <v/>
+      </c>
+      <c r="R236" s="15">
+        <f>IFERROR(L236/F236-1,"")</f>
+        <v/>
+      </c>
+      <c r="S236" s="15">
+        <f>IFERROR(M236/G236-1,"")</f>
+        <v/>
+      </c>
+      <c r="U236" s="16" t="n"/>
+      <c r="V236" s="16" t="n"/>
+      <c r="W236" s="16" t="n"/>
+      <c r="X236" s="16">
+        <f>IFERROR(W236-V236,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="237">
+      <c r="B237" s="13" t="inlineStr">
+        <is>
+          <t>20-39</t>
+        </is>
+      </c>
+      <c r="C237" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D237" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E237" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F237" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G237" s="14">
+        <f>SUM(C237:F237)</f>
+        <v/>
+      </c>
+      <c r="I237" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J237" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K237" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L237" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M237" s="14">
+        <f>SUM(I237:L237)</f>
+        <v/>
+      </c>
+      <c r="O237" s="15">
+        <f>IFERROR(I237/C237-1,"")</f>
+        <v/>
+      </c>
+      <c r="P237" s="15">
+        <f>IFERROR(J237/D237-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q237" s="15">
+        <f>IFERROR(K237/E237-1,"")</f>
+        <v/>
+      </c>
+      <c r="R237" s="15">
+        <f>IFERROR(L237/F237-1,"")</f>
+        <v/>
+      </c>
+      <c r="S237" s="15">
+        <f>IFERROR(M237/G237-1,"")</f>
+        <v/>
+      </c>
+      <c r="U237" s="16" t="n"/>
+      <c r="V237" s="16" t="n"/>
+      <c r="W237" s="16" t="n"/>
+      <c r="X237" s="16">
+        <f>IFERROR(W237-V237,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="238">
+      <c r="B238" s="13" t="inlineStr">
+        <is>
+          <t>40-99</t>
+        </is>
+      </c>
+      <c r="C238" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D238" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E238" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F238" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G238" s="14">
+        <f>SUM(C238:F238)</f>
+        <v/>
+      </c>
+      <c r="I238" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J238" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K238" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L238" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M238" s="14">
+        <f>SUM(I238:L238)</f>
+        <v/>
+      </c>
+      <c r="O238" s="15">
+        <f>IFERROR(I238/C238-1,"")</f>
+        <v/>
+      </c>
+      <c r="P238" s="15">
+        <f>IFERROR(J238/D238-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q238" s="15">
+        <f>IFERROR(K238/E238-1,"")</f>
+        <v/>
+      </c>
+      <c r="R238" s="15">
+        <f>IFERROR(L238/F238-1,"")</f>
+        <v/>
+      </c>
+      <c r="S238" s="15">
+        <f>IFERROR(M238/G238-1,"")</f>
+        <v/>
+      </c>
+      <c r="U238" s="16" t="n"/>
+      <c r="V238" s="16" t="n"/>
+      <c r="W238" s="16" t="n"/>
+      <c r="X238" s="16">
+        <f>IFERROR(W238-V238,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="239">
+      <c r="B239" s="13" t="inlineStr">
+        <is>
+          <t>100+</t>
+        </is>
+      </c>
+      <c r="C239" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D239" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E239" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F239" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G239" s="14">
+        <f>SUM(C239:F239)</f>
+        <v/>
+      </c>
+      <c r="I239" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J239" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K239" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L239" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M239" s="14">
+        <f>SUM(I239:L239)</f>
+        <v/>
+      </c>
+      <c r="O239" s="15">
+        <f>IFERROR(I239/C239-1,"")</f>
+        <v/>
+      </c>
+      <c r="P239" s="15">
+        <f>IFERROR(J239/D239-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q239" s="15">
+        <f>IFERROR(K239/E239-1,"")</f>
+        <v/>
+      </c>
+      <c r="R239" s="15">
+        <f>IFERROR(L239/F239-1,"")</f>
+        <v/>
+      </c>
+      <c r="S239" s="15">
+        <f>IFERROR(M239/G239-1,"")</f>
+        <v/>
+      </c>
+      <c r="U239" s="16" t="n"/>
+      <c r="V239" s="16" t="n"/>
+      <c r="W239" s="16" t="n"/>
+      <c r="X239" s="16">
+        <f>IFERROR(W239-V239,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="240">
+      <c r="B240" s="17" t="inlineStr">
+        <is>
+          <t>overall</t>
+        </is>
+      </c>
+      <c r="C240" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D240" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E240" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F240" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G240" s="18">
+        <f>SUM(C240:F240)</f>
+        <v/>
+      </c>
+      <c r="I240" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J240" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K240" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L240" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M240" s="18">
+        <f>SUM(I240:L240)</f>
+        <v/>
+      </c>
+      <c r="O240" s="19">
+        <f>IFERROR(I240/C240-1,"")</f>
+        <v/>
+      </c>
+      <c r="P240" s="19">
+        <f>IFERROR(J240/D240-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q240" s="19">
+        <f>IFERROR(K240/E240-1,"")</f>
+        <v/>
+      </c>
+      <c r="R240" s="19">
+        <f>IFERROR(L240/F240-1,"")</f>
+        <v/>
+      </c>
+      <c r="S240" s="19">
+        <f>IFERROR(M240/G240-1,"")</f>
+        <v/>
+      </c>
+      <c r="U240" s="20" t="n"/>
+      <c r="V240" s="20" t="n"/>
+      <c r="W240" s="20" t="n"/>
+      <c r="X240" s="20">
+        <f>IFERROR(W240-V240,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="241">
+      <c r="B241" s="12" t="inlineStr">
+        <is>
+          <t>PAYER</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="B242" s="13" t="inlineStr">
+        <is>
+          <t>0-9</t>
+        </is>
+      </c>
+      <c r="C242" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D242" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E242" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F242" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G242" s="14">
+        <f>SUM(C242:F242)</f>
+        <v/>
+      </c>
+      <c r="I242" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J242" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K242" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L242" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M242" s="14">
+        <f>SUM(I242:L242)</f>
+        <v/>
+      </c>
+      <c r="O242" s="15">
+        <f>IFERROR(I242/C242-1,"")</f>
+        <v/>
+      </c>
+      <c r="P242" s="15">
+        <f>IFERROR(J242/D242-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q242" s="15">
+        <f>IFERROR(K242/E242-1,"")</f>
+        <v/>
+      </c>
+      <c r="R242" s="15">
+        <f>IFERROR(L242/F242-1,"")</f>
+        <v/>
+      </c>
+      <c r="S242" s="15">
+        <f>IFERROR(M242/G242-1,"")</f>
+        <v/>
+      </c>
+      <c r="U242" s="16" t="n"/>
+      <c r="V242" s="16" t="n"/>
+      <c r="W242" s="16" t="n"/>
+      <c r="X242" s="16">
+        <f>IFERROR(W242-V242,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="243">
+      <c r="B243" s="13" t="inlineStr">
+        <is>
+          <t>10-19</t>
+        </is>
+      </c>
+      <c r="C243" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D243" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E243" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F243" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G243" s="14">
+        <f>SUM(C243:F243)</f>
+        <v/>
+      </c>
+      <c r="I243" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J243" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K243" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L243" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M243" s="14">
+        <f>SUM(I243:L243)</f>
+        <v/>
+      </c>
+      <c r="O243" s="15">
+        <f>IFERROR(I243/C243-1,"")</f>
+        <v/>
+      </c>
+      <c r="P243" s="15">
+        <f>IFERROR(J243/D243-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q243" s="15">
+        <f>IFERROR(K243/E243-1,"")</f>
+        <v/>
+      </c>
+      <c r="R243" s="15">
+        <f>IFERROR(L243/F243-1,"")</f>
+        <v/>
+      </c>
+      <c r="S243" s="15">
+        <f>IFERROR(M243/G243-1,"")</f>
+        <v/>
+      </c>
+      <c r="U243" s="16" t="n"/>
+      <c r="V243" s="16" t="n"/>
+      <c r="W243" s="16" t="n"/>
+      <c r="X243" s="16">
+        <f>IFERROR(W243-V243,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="244">
+      <c r="B244" s="13" t="inlineStr">
+        <is>
+          <t>20-39</t>
+        </is>
+      </c>
+      <c r="C244" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D244" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E244" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F244" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G244" s="14">
+        <f>SUM(C244:F244)</f>
+        <v/>
+      </c>
+      <c r="I244" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J244" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K244" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L244" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M244" s="14">
+        <f>SUM(I244:L244)</f>
+        <v/>
+      </c>
+      <c r="O244" s="15">
+        <f>IFERROR(I244/C244-1,"")</f>
+        <v/>
+      </c>
+      <c r="P244" s="15">
+        <f>IFERROR(J244/D244-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q244" s="15">
+        <f>IFERROR(K244/E244-1,"")</f>
+        <v/>
+      </c>
+      <c r="R244" s="15">
+        <f>IFERROR(L244/F244-1,"")</f>
+        <v/>
+      </c>
+      <c r="S244" s="15">
+        <f>IFERROR(M244/G244-1,"")</f>
+        <v/>
+      </c>
+      <c r="U244" s="16" t="n"/>
+      <c r="V244" s="16" t="n"/>
+      <c r="W244" s="16" t="n"/>
+      <c r="X244" s="16">
+        <f>IFERROR(W244-V244,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="245">
+      <c r="B245" s="13" t="inlineStr">
+        <is>
+          <t>40-99</t>
+        </is>
+      </c>
+      <c r="C245" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D245" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E245" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F245" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G245" s="14">
+        <f>SUM(C245:F245)</f>
+        <v/>
+      </c>
+      <c r="I245" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J245" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K245" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L245" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M245" s="14">
+        <f>SUM(I245:L245)</f>
+        <v/>
+      </c>
+      <c r="O245" s="15">
+        <f>IFERROR(I245/C245-1,"")</f>
+        <v/>
+      </c>
+      <c r="P245" s="15">
+        <f>IFERROR(J245/D245-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q245" s="15">
+        <f>IFERROR(K245/E245-1,"")</f>
+        <v/>
+      </c>
+      <c r="R245" s="15">
+        <f>IFERROR(L245/F245-1,"")</f>
+        <v/>
+      </c>
+      <c r="S245" s="15">
+        <f>IFERROR(M245/G245-1,"")</f>
+        <v/>
+      </c>
+      <c r="U245" s="16" t="n"/>
+      <c r="V245" s="16" t="n"/>
+      <c r="W245" s="16" t="n"/>
+      <c r="X245" s="16">
+        <f>IFERROR(W245-V245,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="246">
+      <c r="B246" s="13" t="inlineStr">
+        <is>
+          <t>100+</t>
+        </is>
+      </c>
+      <c r="C246" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D246" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E246" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F246" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G246" s="14">
+        <f>SUM(C246:F246)</f>
+        <v/>
+      </c>
+      <c r="I246" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J246" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K246" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L246" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M246" s="14">
+        <f>SUM(I246:L246)</f>
+        <v/>
+      </c>
+      <c r="O246" s="15">
+        <f>IFERROR(I246/C246-1,"")</f>
+        <v/>
+      </c>
+      <c r="P246" s="15">
+        <f>IFERROR(J246/D246-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q246" s="15">
+        <f>IFERROR(K246/E246-1,"")</f>
+        <v/>
+      </c>
+      <c r="R246" s="15">
+        <f>IFERROR(L246/F246-1,"")</f>
+        <v/>
+      </c>
+      <c r="S246" s="15">
+        <f>IFERROR(M246/G246-1,"")</f>
+        <v/>
+      </c>
+      <c r="U246" s="16" t="n"/>
+      <c r="V246" s="16" t="n"/>
+      <c r="W246" s="16" t="n"/>
+      <c r="X246" s="16">
+        <f>IFERROR(W246-V246,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="247">
+      <c r="B247" s="17" t="inlineStr">
+        <is>
+          <t>overall</t>
+        </is>
+      </c>
+      <c r="C247" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D247" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E247" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F247" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G247" s="18">
+        <f>SUM(C247:F247)</f>
+        <v/>
+      </c>
+      <c r="I247" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J247" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K247" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L247" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M247" s="18">
+        <f>SUM(I247:L247)</f>
+        <v/>
+      </c>
+      <c r="O247" s="19">
+        <f>IFERROR(I247/C247-1,"")</f>
+        <v/>
+      </c>
+      <c r="P247" s="19">
+        <f>IFERROR(J247/D247-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q247" s="19">
+        <f>IFERROR(K247/E247-1,"")</f>
+        <v/>
+      </c>
+      <c r="R247" s="19">
+        <f>IFERROR(L247/F247-1,"")</f>
+        <v/>
+      </c>
+      <c r="S247" s="19">
+        <f>IFERROR(M247/G247-1,"")</f>
+        <v/>
+      </c>
+      <c r="U247" s="20" t="n"/>
+      <c r="V247" s="20" t="n"/>
+      <c r="W247" s="20" t="n"/>
+      <c r="X247" s="20">
+        <f>IFERROR(W247-V247,"")</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/display/Sim_per_Segment_v3.xlsx
+++ b/display/Sim_per_Segment_v3.xlsx
@@ -568,7 +568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X247"/>
+  <dimension ref="A1:X361"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -1097,13 +1097,13 @@
         <v>0</v>
       </c>
       <c r="D12" s="18" t="n">
-        <v>21.9041</v>
+        <v>21.8901</v>
       </c>
       <c r="E12" s="18" t="n">
-        <v>371.6886</v>
+        <v>370.792</v>
       </c>
       <c r="F12" s="18" t="n">
-        <v>242.3789</v>
+        <v>241.6529</v>
       </c>
       <c r="G12" s="18">
         <f>SUM(C12:F12)</f>
@@ -1113,13 +1113,13 @@
         <v>0</v>
       </c>
       <c r="J12" s="18" t="n">
-        <v>21.9041</v>
+        <v>21.8901</v>
       </c>
       <c r="K12" s="18" t="n">
-        <v>364.1664</v>
+        <v>363.1251</v>
       </c>
       <c r="L12" s="18" t="n">
-        <v>375.7721</v>
+        <v>374.6754</v>
       </c>
       <c r="M12" s="18">
         <f>SUM(I12:L12)</f>
@@ -1500,13 +1500,13 @@
         <v>0</v>
       </c>
       <c r="D19" s="18" t="n">
-        <v>30.955</v>
+        <v>30.9284</v>
       </c>
       <c r="E19" s="18" t="n">
-        <v>362.0911</v>
+        <v>363.3005</v>
       </c>
       <c r="F19" s="18" t="n">
-        <v>270.1444</v>
+        <v>271.31</v>
       </c>
       <c r="G19" s="18">
         <f>SUM(C19:F19)</f>
@@ -1516,13 +1516,13 @@
         <v>0</v>
       </c>
       <c r="J19" s="18" t="n">
-        <v>30.955</v>
+        <v>30.9284</v>
       </c>
       <c r="K19" s="18" t="n">
-        <v>341.8352</v>
+        <v>343.4372</v>
       </c>
       <c r="L19" s="18" t="n">
-        <v>402.1047</v>
+        <v>403.9433</v>
       </c>
       <c r="M19" s="18">
         <f>SUM(I19:L19)</f>
@@ -2049,13 +2049,13 @@
         <v>0</v>
       </c>
       <c r="D31" s="18" t="n">
-        <v>0.6012999999999999</v>
+        <v>0.6012</v>
       </c>
       <c r="E31" s="18" t="n">
-        <v>4.1734</v>
+        <v>4.1648</v>
       </c>
       <c r="F31" s="18" t="n">
-        <v>3.0204</v>
+        <v>3.017</v>
       </c>
       <c r="G31" s="18">
         <f>SUM(C31:F31)</f>
@@ -2065,13 +2065,13 @@
         <v>0</v>
       </c>
       <c r="J31" s="18" t="n">
-        <v>0.6012999999999999</v>
+        <v>0.6012</v>
       </c>
       <c r="K31" s="18" t="n">
-        <v>4.2946</v>
+        <v>4.2874</v>
       </c>
       <c r="L31" s="18" t="n">
-        <v>11.1435</v>
+        <v>11.1215</v>
       </c>
       <c r="M31" s="18">
         <f>SUM(I31:L31)</f>
@@ -2452,13 +2452,13 @@
         <v>0</v>
       </c>
       <c r="D38" s="18" t="n">
-        <v>0.8313</v>
+        <v>0.8303</v>
       </c>
       <c r="E38" s="18" t="n">
-        <v>3.9897</v>
+        <v>4.0014</v>
       </c>
       <c r="F38" s="18" t="n">
-        <v>3.8346</v>
+        <v>3.8423</v>
       </c>
       <c r="G38" s="18">
         <f>SUM(C38:F38)</f>
@@ -2468,13 +2468,13 @@
         <v>0</v>
       </c>
       <c r="J38" s="18" t="n">
-        <v>0.8313</v>
+        <v>0.8303</v>
       </c>
       <c r="K38" s="18" t="n">
-        <v>3.8667</v>
+        <v>3.8771</v>
       </c>
       <c r="L38" s="18" t="n">
-        <v>12.0483</v>
+        <v>12.0884</v>
       </c>
       <c r="M38" s="18">
         <f>SUM(I38:L38)</f>
@@ -3001,13 +3001,13 @@
         <v>0</v>
       </c>
       <c r="D50" s="18" t="n">
-        <v>0.613</v>
+        <v>0.6129</v>
       </c>
       <c r="E50" s="18" t="n">
-        <v>3.7346</v>
+        <v>3.7261</v>
       </c>
       <c r="F50" s="18" t="n">
-        <v>2.8471</v>
+        <v>2.8425</v>
       </c>
       <c r="G50" s="18">
         <f>SUM(C50:F50)</f>
@@ -3017,13 +3017,13 @@
         <v>0</v>
       </c>
       <c r="J50" s="18" t="n">
-        <v>0.613</v>
+        <v>0.6129</v>
       </c>
       <c r="K50" s="18" t="n">
-        <v>3.7346</v>
+        <v>3.7261</v>
       </c>
       <c r="L50" s="18" t="n">
-        <v>4.823</v>
+        <v>4.8083</v>
       </c>
       <c r="M50" s="18">
         <f>SUM(I50:L50)</f>
@@ -3404,13 +3404,13 @@
         <v>0</v>
       </c>
       <c r="D57" s="18" t="n">
-        <v>0.8532999999999999</v>
+        <v>0.8521</v>
       </c>
       <c r="E57" s="18" t="n">
-        <v>3.5125</v>
+        <v>3.5244</v>
       </c>
       <c r="F57" s="18" t="n">
-        <v>3.5353</v>
+        <v>3.5445</v>
       </c>
       <c r="G57" s="18">
         <f>SUM(C57:F57)</f>
@@ -3420,13 +3420,13 @@
         <v>0</v>
       </c>
       <c r="J57" s="18" t="n">
-        <v>0.8532999999999999</v>
+        <v>0.8521</v>
       </c>
       <c r="K57" s="18" t="n">
-        <v>3.5125</v>
+        <v>3.5244</v>
       </c>
       <c r="L57" s="18" t="n">
-        <v>5.3889</v>
+        <v>5.4169</v>
       </c>
       <c r="M57" s="18">
         <f>SUM(I57:L57)</f>
@@ -3956,10 +3956,10 @@
         <v>0.3483</v>
       </c>
       <c r="E69" s="18" t="n">
-        <v>1.7434</v>
+        <v>1.7393</v>
       </c>
       <c r="F69" s="18" t="n">
-        <v>1.8874</v>
+        <v>1.8839</v>
       </c>
       <c r="G69" s="18">
         <f>SUM(C69:F69)</f>
@@ -3972,10 +3972,10 @@
         <v>0.3483</v>
       </c>
       <c r="K69" s="18" t="n">
-        <v>1.7434</v>
+        <v>1.7393</v>
       </c>
       <c r="L69" s="18" t="n">
-        <v>2.8376</v>
+        <v>2.8262</v>
       </c>
       <c r="M69" s="18">
         <f>SUM(I69:L69)</f>
@@ -4356,13 +4356,13 @@
         <v>0</v>
       </c>
       <c r="D76" s="18" t="n">
-        <v>0.4667</v>
+        <v>0.466</v>
       </c>
       <c r="E76" s="18" t="n">
-        <v>1.5333</v>
+        <v>1.5395</v>
       </c>
       <c r="F76" s="18" t="n">
-        <v>2.5935</v>
+        <v>2.6009</v>
       </c>
       <c r="G76" s="18">
         <f>SUM(C76:F76)</f>
@@ -4372,13 +4372,13 @@
         <v>0</v>
       </c>
       <c r="J76" s="18" t="n">
-        <v>0.4667</v>
+        <v>0.466</v>
       </c>
       <c r="K76" s="18" t="n">
-        <v>1.5333</v>
+        <v>1.5395</v>
       </c>
       <c r="L76" s="18" t="n">
-        <v>3.3767</v>
+        <v>3.3985</v>
       </c>
       <c r="M76" s="18">
         <f>SUM(I76:L76)</f>
@@ -4908,10 +4908,10 @@
         <v>0</v>
       </c>
       <c r="E88" s="18" t="n">
-        <v>4.6144</v>
+        <v>4.599</v>
       </c>
       <c r="F88" s="18" t="n">
-        <v>4.6427</v>
+        <v>4.6395</v>
       </c>
       <c r="G88" s="18">
         <f>SUM(C88:F88)</f>
@@ -4924,10 +4924,10 @@
         <v>0</v>
       </c>
       <c r="K88" s="18" t="n">
-        <v>6.5816</v>
+        <v>6.568</v>
       </c>
       <c r="L88" s="18" t="n">
-        <v>13.4692</v>
+        <v>13.4529</v>
       </c>
       <c r="M88" s="18">
         <f>SUM(I88:L88)</f>
@@ -5311,10 +5311,10 @@
         <v>0</v>
       </c>
       <c r="E95" s="18" t="n">
-        <v>4.131</v>
+        <v>4.1547</v>
       </c>
       <c r="F95" s="18" t="n">
-        <v>5.643</v>
+        <v>5.6492</v>
       </c>
       <c r="G95" s="18">
         <f>SUM(C95:F95)</f>
@@ -5327,10 +5327,10 @@
         <v>0</v>
       </c>
       <c r="K95" s="18" t="n">
-        <v>6.4454</v>
+        <v>6.4644</v>
       </c>
       <c r="L95" s="18" t="n">
-        <v>14.6925</v>
+        <v>14.7205</v>
       </c>
       <c r="M95" s="18">
         <f>SUM(I95:L95)</f>
@@ -5860,10 +5860,10 @@
         <v>0</v>
       </c>
       <c r="E107" s="18" t="n">
-        <v>4.3077</v>
+        <v>4.2922</v>
       </c>
       <c r="F107" s="18" t="n">
-        <v>5.1602</v>
+        <v>5.1572</v>
       </c>
       <c r="G107" s="18">
         <f>SUM(C107:F107)</f>
@@ -5876,10 +5876,10 @@
         <v>0</v>
       </c>
       <c r="K107" s="18" t="n">
-        <v>4.4593</v>
+        <v>4.4453</v>
       </c>
       <c r="L107" s="18" t="n">
-        <v>14.3552</v>
+        <v>14.3417</v>
       </c>
       <c r="M107" s="18">
         <f>SUM(I107:L107)</f>
@@ -6263,10 +6263,10 @@
         <v>0</v>
       </c>
       <c r="E114" s="18" t="n">
-        <v>3.8619</v>
+        <v>3.8858</v>
       </c>
       <c r="F114" s="18" t="n">
-        <v>6.171</v>
+        <v>6.1766</v>
       </c>
       <c r="G114" s="18">
         <f>SUM(C114:F114)</f>
@@ -6279,10 +6279,10 @@
         <v>0</v>
       </c>
       <c r="K114" s="18" t="n">
-        <v>3.7541</v>
+        <v>3.7768</v>
       </c>
       <c r="L114" s="18" t="n">
-        <v>15.8507</v>
+        <v>15.8723</v>
       </c>
       <c r="M114" s="18">
         <f>SUM(I114:L114)</f>
@@ -6812,10 +6812,10 @@
         <v>0</v>
       </c>
       <c r="E126" s="18" t="n">
-        <v>1.3085</v>
+        <v>1.3042</v>
       </c>
       <c r="F126" s="18" t="n">
-        <v>3.1958</v>
+        <v>3.1924</v>
       </c>
       <c r="G126" s="18">
         <f>SUM(C126:F126)</f>
@@ -6828,10 +6828,10 @@
         <v>0</v>
       </c>
       <c r="K126" s="18" t="n">
-        <v>1.3085</v>
+        <v>1.3042</v>
       </c>
       <c r="L126" s="18" t="n">
-        <v>6.951</v>
+        <v>6.942</v>
       </c>
       <c r="M126" s="18">
         <f>SUM(I126:L126)</f>
@@ -7215,10 +7215,10 @@
         <v>0</v>
       </c>
       <c r="E133" s="18" t="n">
-        <v>1.121</v>
+        <v>1.1275</v>
       </c>
       <c r="F133" s="18" t="n">
-        <v>4.1716</v>
+        <v>4.1793</v>
       </c>
       <c r="G133" s="18">
         <f>SUM(C133:F133)</f>
@@ -7231,10 +7231,10 @@
         <v>0</v>
       </c>
       <c r="K133" s="18" t="n">
-        <v>1.121</v>
+        <v>1.1275</v>
       </c>
       <c r="L133" s="18" t="n">
-        <v>8.076499999999999</v>
+        <v>8.093400000000001</v>
       </c>
       <c r="M133" s="18">
         <f>SUM(I133:L133)</f>
@@ -7764,10 +7764,10 @@
         <v>0</v>
       </c>
       <c r="E145" s="18" t="n">
-        <v>17.8217</v>
+        <v>17.8473</v>
       </c>
       <c r="F145" s="18" t="n">
-        <v>11.7762</v>
+        <v>11.7458</v>
       </c>
       <c r="G145" s="18">
         <f>SUM(C145:F145)</f>
@@ -7780,10 +7780,10 @@
         <v>0</v>
       </c>
       <c r="K145" s="18" t="n">
-        <v>17.8217</v>
+        <v>17.8473</v>
       </c>
       <c r="L145" s="18" t="n">
-        <v>7.0648</v>
+        <v>7.0418</v>
       </c>
       <c r="M145" s="18">
         <f>SUM(I145:L145)</f>
@@ -8167,10 +8167,10 @@
         <v>0</v>
       </c>
       <c r="E152" s="18" t="n">
-        <v>14.9079</v>
+        <v>14.8655</v>
       </c>
       <c r="F152" s="18" t="n">
-        <v>16.3107</v>
+        <v>16.3759</v>
       </c>
       <c r="G152" s="18">
         <f>SUM(C152:F152)</f>
@@ -8183,10 +8183,10 @@
         <v>0</v>
       </c>
       <c r="K152" s="18" t="n">
-        <v>14.9079</v>
+        <v>14.8655</v>
       </c>
       <c r="L152" s="18" t="n">
-        <v>12.4825</v>
+        <v>12.5328</v>
       </c>
       <c r="M152" s="18">
         <f>SUM(I152:L152)</f>
@@ -8716,10 +8716,10 @@
         <v>0</v>
       </c>
       <c r="E164" s="18" t="n">
-        <v>9.9716</v>
+        <v>9.9762</v>
       </c>
       <c r="F164" s="18" t="n">
-        <v>25.5101</v>
+        <v>25.4827</v>
       </c>
       <c r="G164" s="18">
         <f>SUM(C164:F164)</f>
@@ -8732,10 +8732,10 @@
         <v>0</v>
       </c>
       <c r="K164" s="18" t="n">
-        <v>9.9716</v>
+        <v>9.9762</v>
       </c>
       <c r="L164" s="18" t="n">
-        <v>22.6206</v>
+        <v>22.5912</v>
       </c>
       <c r="M164" s="18">
         <f>SUM(I164:L164)</f>
@@ -9119,10 +9119,10 @@
         <v>0</v>
       </c>
       <c r="E171" s="18" t="n">
-        <v>11.3315</v>
+        <v>11.3105</v>
       </c>
       <c r="F171" s="18" t="n">
-        <v>32.2613</v>
+        <v>32.3294</v>
       </c>
       <c r="G171" s="18">
         <f>SUM(C171:F171)</f>
@@ -9135,10 +9135,10 @@
         <v>0</v>
       </c>
       <c r="K171" s="18" t="n">
-        <v>11.3315</v>
+        <v>11.3105</v>
       </c>
       <c r="L171" s="18" t="n">
-        <v>29.688</v>
+        <v>29.7603</v>
       </c>
       <c r="M171" s="18">
         <f>SUM(I171:L171)</f>
@@ -9668,10 +9668,10 @@
         <v>0</v>
       </c>
       <c r="E183" s="18" t="n">
-        <v>8.446899999999999</v>
+        <v>8.4466</v>
       </c>
       <c r="F183" s="18" t="n">
-        <v>31.575</v>
+        <v>31.5319</v>
       </c>
       <c r="G183" s="18">
         <f>SUM(C183:F183)</f>
@@ -9684,10 +9684,10 @@
         <v>0</v>
       </c>
       <c r="K183" s="18" t="n">
-        <v>8.446899999999999</v>
+        <v>8.4466</v>
       </c>
       <c r="L183" s="18" t="n">
-        <v>39.1184</v>
+        <v>39.0549</v>
       </c>
       <c r="M183" s="18">
         <f>SUM(I183:L183)</f>
@@ -10071,10 +10071,10 @@
         <v>0</v>
       </c>
       <c r="E190" s="18" t="n">
-        <v>9.732900000000001</v>
+        <v>9.720599999999999</v>
       </c>
       <c r="F190" s="18" t="n">
-        <v>35.411</v>
+        <v>35.5</v>
       </c>
       <c r="G190" s="18">
         <f>SUM(C190:F190)</f>
@@ -10087,10 +10087,10 @@
         <v>0</v>
       </c>
       <c r="K190" s="18" t="n">
-        <v>9.732900000000001</v>
+        <v>9.720599999999999</v>
       </c>
       <c r="L190" s="18" t="n">
-        <v>43.0662</v>
+        <v>43.1969</v>
       </c>
       <c r="M190" s="18">
         <f>SUM(I190:L190)</f>
@@ -10617,13 +10617,13 @@
         <v>0</v>
       </c>
       <c r="D202" s="18" t="n">
-        <v>7.4016</v>
+        <v>7.3969</v>
       </c>
       <c r="E202" s="18" t="n">
-        <v>298.5914</v>
+        <v>297.9607</v>
       </c>
       <c r="F202" s="18" t="n">
-        <v>289.469</v>
+        <v>289.2579</v>
       </c>
       <c r="G202" s="18">
         <f>SUM(C202:F202)</f>
@@ -10633,13 +10633,13 @@
         <v>0</v>
       </c>
       <c r="J202" s="18" t="n">
-        <v>7.4016</v>
+        <v>7.3969</v>
       </c>
       <c r="K202" s="18" t="n">
-        <v>409.5988</v>
+        <v>408.93</v>
       </c>
       <c r="L202" s="18" t="n">
-        <v>416.9442</v>
+        <v>416.4665</v>
       </c>
       <c r="M202" s="18">
         <f>SUM(I202:L202)</f>
@@ -11020,13 +11020,13 @@
         <v>0</v>
       </c>
       <c r="D209" s="18" t="n">
-        <v>10.4108</v>
+        <v>10.4019</v>
       </c>
       <c r="E209" s="18" t="n">
-        <v>297.8021</v>
+        <v>298.6281</v>
       </c>
       <c r="F209" s="18" t="n">
-        <v>392.6539</v>
+        <v>393.224</v>
       </c>
       <c r="G209" s="18">
         <f>SUM(C209:F209)</f>
@@ -11036,13 +11036,13 @@
         <v>0</v>
       </c>
       <c r="J209" s="18" t="n">
-        <v>10.4108</v>
+        <v>10.4019</v>
       </c>
       <c r="K209" s="18" t="n">
-        <v>399.9511</v>
+        <v>400.8304</v>
       </c>
       <c r="L209" s="18" t="n">
-        <v>524.1641</v>
+        <v>525.1928</v>
       </c>
       <c r="M209" s="18">
         <f>SUM(I209:L209)</f>
@@ -12980,6 +12980,5718 @@
         <v/>
       </c>
     </row>
+    <row r="250">
+      <c r="B250" s="2" t="inlineStr">
+        <is>
+          <t>◆ 1-star Pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="C251" s="3" t="inlineStr">
+        <is>
+          <t>◄ CURRENT (actuals: data + calc) ►</t>
+        </is>
+      </c>
+      <c r="D251" s="3" t="n"/>
+      <c r="E251" s="3" t="n"/>
+      <c r="F251" s="3" t="n"/>
+      <c r="G251" s="3" t="n"/>
+      <c r="I251" s="4" t="inlineStr">
+        <is>
+          <t>◄ SIMULATED (EcoGainsSim v4) ►</t>
+        </is>
+      </c>
+      <c r="J251" s="4" t="n"/>
+      <c r="K251" s="4" t="n"/>
+      <c r="L251" s="4" t="n"/>
+      <c r="M251" s="4" t="n"/>
+      <c r="O251" s="5" t="inlineStr">
+        <is>
+          <t>Δ</t>
+        </is>
+      </c>
+      <c r="P251" s="5" t="n"/>
+      <c r="Q251" s="5" t="n"/>
+      <c r="R251" s="5" t="n"/>
+      <c r="S251" s="5" t="n"/>
+      <c r="U251" s="6" t="inlineStr">
+        <is>
+          <t>◄ NET / earner (spend held constant) ►</t>
+        </is>
+      </c>
+      <c r="V251" s="6" t="n"/>
+      <c r="W251" s="6" t="n"/>
+      <c r="X251" s="6" t="n"/>
+    </row>
+    <row r="252">
+      <c r="B252" s="7" t="inlineStr">
+        <is>
+          <t>Segment</t>
+        </is>
+      </c>
+      <c r="C252" s="8" t="inlineStr">
+        <is>
+          <t>PAID</t>
+        </is>
+      </c>
+      <c r="D252" s="8" t="inlineStr">
+        <is>
+          <t>ADS</t>
+        </is>
+      </c>
+      <c r="E252" s="8" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="F252" s="8" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="G252" s="8" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="I252" s="9" t="inlineStr">
+        <is>
+          <t>PAID</t>
+        </is>
+      </c>
+      <c r="J252" s="9" t="inlineStr">
+        <is>
+          <t>ADS</t>
+        </is>
+      </c>
+      <c r="K252" s="9" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="L252" s="9" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="M252" s="9" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="O252" s="10" t="inlineStr">
+        <is>
+          <t>PAID</t>
+        </is>
+      </c>
+      <c r="P252" s="10" t="inlineStr">
+        <is>
+          <t>ADS</t>
+        </is>
+      </c>
+      <c r="Q252" s="10" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="R252" s="10" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="S252" s="10" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="U252" s="11" t="inlineStr">
+        <is>
+          <t>cur spend</t>
+        </is>
+      </c>
+      <c r="V252" s="11" t="inlineStr">
+        <is>
+          <t>cur net</t>
+        </is>
+      </c>
+      <c r="W252" s="11" t="inlineStr">
+        <is>
+          <t>new net</t>
+        </is>
+      </c>
+      <c r="X252" s="11" t="inlineStr">
+        <is>
+          <t>net Δ</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="B253" s="12" t="inlineStr">
+        <is>
+          <t>NONPAYER</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="B254" s="13" t="inlineStr">
+        <is>
+          <t>0-9</t>
+        </is>
+      </c>
+      <c r="C254" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D254" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E254" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F254" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G254" s="14">
+        <f>SUM(C254:F254)</f>
+        <v/>
+      </c>
+      <c r="I254" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J254" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K254" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L254" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M254" s="14">
+        <f>SUM(I254:L254)</f>
+        <v/>
+      </c>
+      <c r="O254" s="15">
+        <f>IFERROR(I254/C254-1,"")</f>
+        <v/>
+      </c>
+      <c r="P254" s="15">
+        <f>IFERROR(J254/D254-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q254" s="15">
+        <f>IFERROR(K254/E254-1,"")</f>
+        <v/>
+      </c>
+      <c r="R254" s="15">
+        <f>IFERROR(L254/F254-1,"")</f>
+        <v/>
+      </c>
+      <c r="S254" s="15">
+        <f>IFERROR(M254/G254-1,"")</f>
+        <v/>
+      </c>
+      <c r="U254" s="16" t="n"/>
+      <c r="V254" s="16" t="n"/>
+      <c r="W254" s="16" t="n"/>
+      <c r="X254" s="16">
+        <f>IFERROR(W254-V254,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="255">
+      <c r="B255" s="13" t="inlineStr">
+        <is>
+          <t>10-19</t>
+        </is>
+      </c>
+      <c r="C255" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D255" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E255" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F255" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G255" s="14">
+        <f>SUM(C255:F255)</f>
+        <v/>
+      </c>
+      <c r="I255" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J255" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K255" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L255" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M255" s="14">
+        <f>SUM(I255:L255)</f>
+        <v/>
+      </c>
+      <c r="O255" s="15">
+        <f>IFERROR(I255/C255-1,"")</f>
+        <v/>
+      </c>
+      <c r="P255" s="15">
+        <f>IFERROR(J255/D255-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q255" s="15">
+        <f>IFERROR(K255/E255-1,"")</f>
+        <v/>
+      </c>
+      <c r="R255" s="15">
+        <f>IFERROR(L255/F255-1,"")</f>
+        <v/>
+      </c>
+      <c r="S255" s="15">
+        <f>IFERROR(M255/G255-1,"")</f>
+        <v/>
+      </c>
+      <c r="U255" s="16" t="n"/>
+      <c r="V255" s="16" t="n"/>
+      <c r="W255" s="16" t="n"/>
+      <c r="X255" s="16">
+        <f>IFERROR(W255-V255,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="256">
+      <c r="B256" s="13" t="inlineStr">
+        <is>
+          <t>20-39</t>
+        </is>
+      </c>
+      <c r="C256" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D256" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E256" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F256" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G256" s="14">
+        <f>SUM(C256:F256)</f>
+        <v/>
+      </c>
+      <c r="I256" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J256" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K256" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L256" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M256" s="14">
+        <f>SUM(I256:L256)</f>
+        <v/>
+      </c>
+      <c r="O256" s="15">
+        <f>IFERROR(I256/C256-1,"")</f>
+        <v/>
+      </c>
+      <c r="P256" s="15">
+        <f>IFERROR(J256/D256-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q256" s="15">
+        <f>IFERROR(K256/E256-1,"")</f>
+        <v/>
+      </c>
+      <c r="R256" s="15">
+        <f>IFERROR(L256/F256-1,"")</f>
+        <v/>
+      </c>
+      <c r="S256" s="15">
+        <f>IFERROR(M256/G256-1,"")</f>
+        <v/>
+      </c>
+      <c r="U256" s="16" t="n"/>
+      <c r="V256" s="16" t="n"/>
+      <c r="W256" s="16" t="n"/>
+      <c r="X256" s="16">
+        <f>IFERROR(W256-V256,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="257">
+      <c r="B257" s="13" t="inlineStr">
+        <is>
+          <t>40-99</t>
+        </is>
+      </c>
+      <c r="C257" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D257" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E257" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F257" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G257" s="14">
+        <f>SUM(C257:F257)</f>
+        <v/>
+      </c>
+      <c r="I257" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J257" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K257" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L257" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M257" s="14">
+        <f>SUM(I257:L257)</f>
+        <v/>
+      </c>
+      <c r="O257" s="15">
+        <f>IFERROR(I257/C257-1,"")</f>
+        <v/>
+      </c>
+      <c r="P257" s="15">
+        <f>IFERROR(J257/D257-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q257" s="15">
+        <f>IFERROR(K257/E257-1,"")</f>
+        <v/>
+      </c>
+      <c r="R257" s="15">
+        <f>IFERROR(L257/F257-1,"")</f>
+        <v/>
+      </c>
+      <c r="S257" s="15">
+        <f>IFERROR(M257/G257-1,"")</f>
+        <v/>
+      </c>
+      <c r="U257" s="16" t="n"/>
+      <c r="V257" s="16" t="n"/>
+      <c r="W257" s="16" t="n"/>
+      <c r="X257" s="16">
+        <f>IFERROR(W257-V257,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="258">
+      <c r="B258" s="13" t="inlineStr">
+        <is>
+          <t>100+</t>
+        </is>
+      </c>
+      <c r="C258" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D258" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E258" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F258" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G258" s="14">
+        <f>SUM(C258:F258)</f>
+        <v/>
+      </c>
+      <c r="I258" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J258" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K258" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L258" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M258" s="14">
+        <f>SUM(I258:L258)</f>
+        <v/>
+      </c>
+      <c r="O258" s="15">
+        <f>IFERROR(I258/C258-1,"")</f>
+        <v/>
+      </c>
+      <c r="P258" s="15">
+        <f>IFERROR(J258/D258-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q258" s="15">
+        <f>IFERROR(K258/E258-1,"")</f>
+        <v/>
+      </c>
+      <c r="R258" s="15">
+        <f>IFERROR(L258/F258-1,"")</f>
+        <v/>
+      </c>
+      <c r="S258" s="15">
+        <f>IFERROR(M258/G258-1,"")</f>
+        <v/>
+      </c>
+      <c r="U258" s="16" t="n"/>
+      <c r="V258" s="16" t="n"/>
+      <c r="W258" s="16" t="n"/>
+      <c r="X258" s="16">
+        <f>IFERROR(W258-V258,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="259">
+      <c r="B259" s="17" t="inlineStr">
+        <is>
+          <t>overall</t>
+        </is>
+      </c>
+      <c r="C259" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D259" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E259" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F259" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G259" s="18">
+        <f>SUM(C259:F259)</f>
+        <v/>
+      </c>
+      <c r="I259" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J259" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K259" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L259" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M259" s="18">
+        <f>SUM(I259:L259)</f>
+        <v/>
+      </c>
+      <c r="O259" s="19">
+        <f>IFERROR(I259/C259-1,"")</f>
+        <v/>
+      </c>
+      <c r="P259" s="19">
+        <f>IFERROR(J259/D259-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q259" s="19">
+        <f>IFERROR(K259/E259-1,"")</f>
+        <v/>
+      </c>
+      <c r="R259" s="19">
+        <f>IFERROR(L259/F259-1,"")</f>
+        <v/>
+      </c>
+      <c r="S259" s="19">
+        <f>IFERROR(M259/G259-1,"")</f>
+        <v/>
+      </c>
+      <c r="U259" s="20" t="n"/>
+      <c r="V259" s="20" t="n"/>
+      <c r="W259" s="20" t="n"/>
+      <c r="X259" s="20">
+        <f>IFERROR(W259-V259,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="260">
+      <c r="B260" s="12" t="inlineStr">
+        <is>
+          <t>PAYER</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="B261" s="13" t="inlineStr">
+        <is>
+          <t>0-9</t>
+        </is>
+      </c>
+      <c r="C261" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D261" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E261" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F261" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G261" s="14">
+        <f>SUM(C261:F261)</f>
+        <v/>
+      </c>
+      <c r="I261" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J261" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K261" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L261" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M261" s="14">
+        <f>SUM(I261:L261)</f>
+        <v/>
+      </c>
+      <c r="O261" s="15">
+        <f>IFERROR(I261/C261-1,"")</f>
+        <v/>
+      </c>
+      <c r="P261" s="15">
+        <f>IFERROR(J261/D261-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q261" s="15">
+        <f>IFERROR(K261/E261-1,"")</f>
+        <v/>
+      </c>
+      <c r="R261" s="15">
+        <f>IFERROR(L261/F261-1,"")</f>
+        <v/>
+      </c>
+      <c r="S261" s="15">
+        <f>IFERROR(M261/G261-1,"")</f>
+        <v/>
+      </c>
+      <c r="U261" s="16" t="n"/>
+      <c r="V261" s="16" t="n"/>
+      <c r="W261" s="16" t="n"/>
+      <c r="X261" s="16">
+        <f>IFERROR(W261-V261,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="262">
+      <c r="B262" s="13" t="inlineStr">
+        <is>
+          <t>10-19</t>
+        </is>
+      </c>
+      <c r="C262" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D262" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E262" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F262" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G262" s="14">
+        <f>SUM(C262:F262)</f>
+        <v/>
+      </c>
+      <c r="I262" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J262" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K262" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L262" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M262" s="14">
+        <f>SUM(I262:L262)</f>
+        <v/>
+      </c>
+      <c r="O262" s="15">
+        <f>IFERROR(I262/C262-1,"")</f>
+        <v/>
+      </c>
+      <c r="P262" s="15">
+        <f>IFERROR(J262/D262-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q262" s="15">
+        <f>IFERROR(K262/E262-1,"")</f>
+        <v/>
+      </c>
+      <c r="R262" s="15">
+        <f>IFERROR(L262/F262-1,"")</f>
+        <v/>
+      </c>
+      <c r="S262" s="15">
+        <f>IFERROR(M262/G262-1,"")</f>
+        <v/>
+      </c>
+      <c r="U262" s="16" t="n"/>
+      <c r="V262" s="16" t="n"/>
+      <c r="W262" s="16" t="n"/>
+      <c r="X262" s="16">
+        <f>IFERROR(W262-V262,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="263">
+      <c r="B263" s="13" t="inlineStr">
+        <is>
+          <t>20-39</t>
+        </is>
+      </c>
+      <c r="C263" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D263" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E263" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F263" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G263" s="14">
+        <f>SUM(C263:F263)</f>
+        <v/>
+      </c>
+      <c r="I263" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J263" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K263" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L263" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M263" s="14">
+        <f>SUM(I263:L263)</f>
+        <v/>
+      </c>
+      <c r="O263" s="15">
+        <f>IFERROR(I263/C263-1,"")</f>
+        <v/>
+      </c>
+      <c r="P263" s="15">
+        <f>IFERROR(J263/D263-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q263" s="15">
+        <f>IFERROR(K263/E263-1,"")</f>
+        <v/>
+      </c>
+      <c r="R263" s="15">
+        <f>IFERROR(L263/F263-1,"")</f>
+        <v/>
+      </c>
+      <c r="S263" s="15">
+        <f>IFERROR(M263/G263-1,"")</f>
+        <v/>
+      </c>
+      <c r="U263" s="16" t="n"/>
+      <c r="V263" s="16" t="n"/>
+      <c r="W263" s="16" t="n"/>
+      <c r="X263" s="16">
+        <f>IFERROR(W263-V263,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="264">
+      <c r="B264" s="13" t="inlineStr">
+        <is>
+          <t>40-99</t>
+        </is>
+      </c>
+      <c r="C264" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D264" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E264" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F264" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G264" s="14">
+        <f>SUM(C264:F264)</f>
+        <v/>
+      </c>
+      <c r="I264" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J264" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K264" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L264" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M264" s="14">
+        <f>SUM(I264:L264)</f>
+        <v/>
+      </c>
+      <c r="O264" s="15">
+        <f>IFERROR(I264/C264-1,"")</f>
+        <v/>
+      </c>
+      <c r="P264" s="15">
+        <f>IFERROR(J264/D264-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q264" s="15">
+        <f>IFERROR(K264/E264-1,"")</f>
+        <v/>
+      </c>
+      <c r="R264" s="15">
+        <f>IFERROR(L264/F264-1,"")</f>
+        <v/>
+      </c>
+      <c r="S264" s="15">
+        <f>IFERROR(M264/G264-1,"")</f>
+        <v/>
+      </c>
+      <c r="U264" s="16" t="n"/>
+      <c r="V264" s="16" t="n"/>
+      <c r="W264" s="16" t="n"/>
+      <c r="X264" s="16">
+        <f>IFERROR(W264-V264,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="265">
+      <c r="B265" s="13" t="inlineStr">
+        <is>
+          <t>100+</t>
+        </is>
+      </c>
+      <c r="C265" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D265" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E265" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F265" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G265" s="14">
+        <f>SUM(C265:F265)</f>
+        <v/>
+      </c>
+      <c r="I265" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J265" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K265" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L265" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M265" s="14">
+        <f>SUM(I265:L265)</f>
+        <v/>
+      </c>
+      <c r="O265" s="15">
+        <f>IFERROR(I265/C265-1,"")</f>
+        <v/>
+      </c>
+      <c r="P265" s="15">
+        <f>IFERROR(J265/D265-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q265" s="15">
+        <f>IFERROR(K265/E265-1,"")</f>
+        <v/>
+      </c>
+      <c r="R265" s="15">
+        <f>IFERROR(L265/F265-1,"")</f>
+        <v/>
+      </c>
+      <c r="S265" s="15">
+        <f>IFERROR(M265/G265-1,"")</f>
+        <v/>
+      </c>
+      <c r="U265" s="16" t="n"/>
+      <c r="V265" s="16" t="n"/>
+      <c r="W265" s="16" t="n"/>
+      <c r="X265" s="16">
+        <f>IFERROR(W265-V265,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="266">
+      <c r="B266" s="17" t="inlineStr">
+        <is>
+          <t>overall</t>
+        </is>
+      </c>
+      <c r="C266" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D266" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E266" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F266" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G266" s="18">
+        <f>SUM(C266:F266)</f>
+        <v/>
+      </c>
+      <c r="I266" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J266" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K266" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L266" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M266" s="18">
+        <f>SUM(I266:L266)</f>
+        <v/>
+      </c>
+      <c r="O266" s="19">
+        <f>IFERROR(I266/C266-1,"")</f>
+        <v/>
+      </c>
+      <c r="P266" s="19">
+        <f>IFERROR(J266/D266-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q266" s="19">
+        <f>IFERROR(K266/E266-1,"")</f>
+        <v/>
+      </c>
+      <c r="R266" s="19">
+        <f>IFERROR(L266/F266-1,"")</f>
+        <v/>
+      </c>
+      <c r="S266" s="19">
+        <f>IFERROR(M266/G266-1,"")</f>
+        <v/>
+      </c>
+      <c r="U266" s="20" t="n"/>
+      <c r="V266" s="20" t="n"/>
+      <c r="W266" s="20" t="n"/>
+      <c r="X266" s="20">
+        <f>IFERROR(W266-V266,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="269">
+      <c r="B269" s="2" t="inlineStr">
+        <is>
+          <t>◆ 2-star Pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="C270" s="3" t="inlineStr">
+        <is>
+          <t>◄ CURRENT (actuals: data + calc) ►</t>
+        </is>
+      </c>
+      <c r="D270" s="3" t="n"/>
+      <c r="E270" s="3" t="n"/>
+      <c r="F270" s="3" t="n"/>
+      <c r="G270" s="3" t="n"/>
+      <c r="I270" s="4" t="inlineStr">
+        <is>
+          <t>◄ SIMULATED (EcoGainsSim v4) ►</t>
+        </is>
+      </c>
+      <c r="J270" s="4" t="n"/>
+      <c r="K270" s="4" t="n"/>
+      <c r="L270" s="4" t="n"/>
+      <c r="M270" s="4" t="n"/>
+      <c r="O270" s="5" t="inlineStr">
+        <is>
+          <t>Δ</t>
+        </is>
+      </c>
+      <c r="P270" s="5" t="n"/>
+      <c r="Q270" s="5" t="n"/>
+      <c r="R270" s="5" t="n"/>
+      <c r="S270" s="5" t="n"/>
+      <c r="U270" s="6" t="inlineStr">
+        <is>
+          <t>◄ NET / earner (spend held constant) ►</t>
+        </is>
+      </c>
+      <c r="V270" s="6" t="n"/>
+      <c r="W270" s="6" t="n"/>
+      <c r="X270" s="6" t="n"/>
+    </row>
+    <row r="271">
+      <c r="B271" s="7" t="inlineStr">
+        <is>
+          <t>Segment</t>
+        </is>
+      </c>
+      <c r="C271" s="8" t="inlineStr">
+        <is>
+          <t>PAID</t>
+        </is>
+      </c>
+      <c r="D271" s="8" t="inlineStr">
+        <is>
+          <t>ADS</t>
+        </is>
+      </c>
+      <c r="E271" s="8" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="F271" s="8" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="G271" s="8" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="I271" s="9" t="inlineStr">
+        <is>
+          <t>PAID</t>
+        </is>
+      </c>
+      <c r="J271" s="9" t="inlineStr">
+        <is>
+          <t>ADS</t>
+        </is>
+      </c>
+      <c r="K271" s="9" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="L271" s="9" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="M271" s="9" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="O271" s="10" t="inlineStr">
+        <is>
+          <t>PAID</t>
+        </is>
+      </c>
+      <c r="P271" s="10" t="inlineStr">
+        <is>
+          <t>ADS</t>
+        </is>
+      </c>
+      <c r="Q271" s="10" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="R271" s="10" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="S271" s="10" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="U271" s="11" t="inlineStr">
+        <is>
+          <t>cur spend</t>
+        </is>
+      </c>
+      <c r="V271" s="11" t="inlineStr">
+        <is>
+          <t>cur net</t>
+        </is>
+      </c>
+      <c r="W271" s="11" t="inlineStr">
+        <is>
+          <t>new net</t>
+        </is>
+      </c>
+      <c r="X271" s="11" t="inlineStr">
+        <is>
+          <t>net Δ</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="B272" s="12" t="inlineStr">
+        <is>
+          <t>NONPAYER</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="B273" s="13" t="inlineStr">
+        <is>
+          <t>0-9</t>
+        </is>
+      </c>
+      <c r="C273" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D273" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E273" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F273" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G273" s="14">
+        <f>SUM(C273:F273)</f>
+        <v/>
+      </c>
+      <c r="I273" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J273" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K273" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L273" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M273" s="14">
+        <f>SUM(I273:L273)</f>
+        <v/>
+      </c>
+      <c r="O273" s="15">
+        <f>IFERROR(I273/C273-1,"")</f>
+        <v/>
+      </c>
+      <c r="P273" s="15">
+        <f>IFERROR(J273/D273-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q273" s="15">
+        <f>IFERROR(K273/E273-1,"")</f>
+        <v/>
+      </c>
+      <c r="R273" s="15">
+        <f>IFERROR(L273/F273-1,"")</f>
+        <v/>
+      </c>
+      <c r="S273" s="15">
+        <f>IFERROR(M273/G273-1,"")</f>
+        <v/>
+      </c>
+      <c r="U273" s="16" t="n"/>
+      <c r="V273" s="16" t="n"/>
+      <c r="W273" s="16" t="n"/>
+      <c r="X273" s="16">
+        <f>IFERROR(W273-V273,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="274">
+      <c r="B274" s="13" t="inlineStr">
+        <is>
+          <t>10-19</t>
+        </is>
+      </c>
+      <c r="C274" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D274" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E274" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F274" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G274" s="14">
+        <f>SUM(C274:F274)</f>
+        <v/>
+      </c>
+      <c r="I274" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J274" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K274" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L274" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M274" s="14">
+        <f>SUM(I274:L274)</f>
+        <v/>
+      </c>
+      <c r="O274" s="15">
+        <f>IFERROR(I274/C274-1,"")</f>
+        <v/>
+      </c>
+      <c r="P274" s="15">
+        <f>IFERROR(J274/D274-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q274" s="15">
+        <f>IFERROR(K274/E274-1,"")</f>
+        <v/>
+      </c>
+      <c r="R274" s="15">
+        <f>IFERROR(L274/F274-1,"")</f>
+        <v/>
+      </c>
+      <c r="S274" s="15">
+        <f>IFERROR(M274/G274-1,"")</f>
+        <v/>
+      </c>
+      <c r="U274" s="16" t="n"/>
+      <c r="V274" s="16" t="n"/>
+      <c r="W274" s="16" t="n"/>
+      <c r="X274" s="16">
+        <f>IFERROR(W274-V274,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="275">
+      <c r="B275" s="13" t="inlineStr">
+        <is>
+          <t>20-39</t>
+        </is>
+      </c>
+      <c r="C275" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D275" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E275" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F275" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G275" s="14">
+        <f>SUM(C275:F275)</f>
+        <v/>
+      </c>
+      <c r="I275" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J275" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K275" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L275" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M275" s="14">
+        <f>SUM(I275:L275)</f>
+        <v/>
+      </c>
+      <c r="O275" s="15">
+        <f>IFERROR(I275/C275-1,"")</f>
+        <v/>
+      </c>
+      <c r="P275" s="15">
+        <f>IFERROR(J275/D275-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q275" s="15">
+        <f>IFERROR(K275/E275-1,"")</f>
+        <v/>
+      </c>
+      <c r="R275" s="15">
+        <f>IFERROR(L275/F275-1,"")</f>
+        <v/>
+      </c>
+      <c r="S275" s="15">
+        <f>IFERROR(M275/G275-1,"")</f>
+        <v/>
+      </c>
+      <c r="U275" s="16" t="n"/>
+      <c r="V275" s="16" t="n"/>
+      <c r="W275" s="16" t="n"/>
+      <c r="X275" s="16">
+        <f>IFERROR(W275-V275,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="276">
+      <c r="B276" s="13" t="inlineStr">
+        <is>
+          <t>40-99</t>
+        </is>
+      </c>
+      <c r="C276" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D276" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E276" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F276" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G276" s="14">
+        <f>SUM(C276:F276)</f>
+        <v/>
+      </c>
+      <c r="I276" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J276" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K276" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L276" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M276" s="14">
+        <f>SUM(I276:L276)</f>
+        <v/>
+      </c>
+      <c r="O276" s="15">
+        <f>IFERROR(I276/C276-1,"")</f>
+        <v/>
+      </c>
+      <c r="P276" s="15">
+        <f>IFERROR(J276/D276-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q276" s="15">
+        <f>IFERROR(K276/E276-1,"")</f>
+        <v/>
+      </c>
+      <c r="R276" s="15">
+        <f>IFERROR(L276/F276-1,"")</f>
+        <v/>
+      </c>
+      <c r="S276" s="15">
+        <f>IFERROR(M276/G276-1,"")</f>
+        <v/>
+      </c>
+      <c r="U276" s="16" t="n"/>
+      <c r="V276" s="16" t="n"/>
+      <c r="W276" s="16" t="n"/>
+      <c r="X276" s="16">
+        <f>IFERROR(W276-V276,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="277">
+      <c r="B277" s="13" t="inlineStr">
+        <is>
+          <t>100+</t>
+        </is>
+      </c>
+      <c r="C277" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D277" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E277" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F277" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G277" s="14">
+        <f>SUM(C277:F277)</f>
+        <v/>
+      </c>
+      <c r="I277" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J277" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K277" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L277" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M277" s="14">
+        <f>SUM(I277:L277)</f>
+        <v/>
+      </c>
+      <c r="O277" s="15">
+        <f>IFERROR(I277/C277-1,"")</f>
+        <v/>
+      </c>
+      <c r="P277" s="15">
+        <f>IFERROR(J277/D277-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q277" s="15">
+        <f>IFERROR(K277/E277-1,"")</f>
+        <v/>
+      </c>
+      <c r="R277" s="15">
+        <f>IFERROR(L277/F277-1,"")</f>
+        <v/>
+      </c>
+      <c r="S277" s="15">
+        <f>IFERROR(M277/G277-1,"")</f>
+        <v/>
+      </c>
+      <c r="U277" s="16" t="n"/>
+      <c r="V277" s="16" t="n"/>
+      <c r="W277" s="16" t="n"/>
+      <c r="X277" s="16">
+        <f>IFERROR(W277-V277,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="278">
+      <c r="B278" s="17" t="inlineStr">
+        <is>
+          <t>overall</t>
+        </is>
+      </c>
+      <c r="C278" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D278" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E278" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F278" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G278" s="18">
+        <f>SUM(C278:F278)</f>
+        <v/>
+      </c>
+      <c r="I278" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J278" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K278" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L278" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M278" s="18">
+        <f>SUM(I278:L278)</f>
+        <v/>
+      </c>
+      <c r="O278" s="19">
+        <f>IFERROR(I278/C278-1,"")</f>
+        <v/>
+      </c>
+      <c r="P278" s="19">
+        <f>IFERROR(J278/D278-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q278" s="19">
+        <f>IFERROR(K278/E278-1,"")</f>
+        <v/>
+      </c>
+      <c r="R278" s="19">
+        <f>IFERROR(L278/F278-1,"")</f>
+        <v/>
+      </c>
+      <c r="S278" s="19">
+        <f>IFERROR(M278/G278-1,"")</f>
+        <v/>
+      </c>
+      <c r="U278" s="20" t="n"/>
+      <c r="V278" s="20" t="n"/>
+      <c r="W278" s="20" t="n"/>
+      <c r="X278" s="20">
+        <f>IFERROR(W278-V278,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="279">
+      <c r="B279" s="12" t="inlineStr">
+        <is>
+          <t>PAYER</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="B280" s="13" t="inlineStr">
+        <is>
+          <t>0-9</t>
+        </is>
+      </c>
+      <c r="C280" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D280" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E280" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F280" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G280" s="14">
+        <f>SUM(C280:F280)</f>
+        <v/>
+      </c>
+      <c r="I280" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J280" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K280" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L280" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M280" s="14">
+        <f>SUM(I280:L280)</f>
+        <v/>
+      </c>
+      <c r="O280" s="15">
+        <f>IFERROR(I280/C280-1,"")</f>
+        <v/>
+      </c>
+      <c r="P280" s="15">
+        <f>IFERROR(J280/D280-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q280" s="15">
+        <f>IFERROR(K280/E280-1,"")</f>
+        <v/>
+      </c>
+      <c r="R280" s="15">
+        <f>IFERROR(L280/F280-1,"")</f>
+        <v/>
+      </c>
+      <c r="S280" s="15">
+        <f>IFERROR(M280/G280-1,"")</f>
+        <v/>
+      </c>
+      <c r="U280" s="16" t="n"/>
+      <c r="V280" s="16" t="n"/>
+      <c r="W280" s="16" t="n"/>
+      <c r="X280" s="16">
+        <f>IFERROR(W280-V280,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="281">
+      <c r="B281" s="13" t="inlineStr">
+        <is>
+          <t>10-19</t>
+        </is>
+      </c>
+      <c r="C281" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D281" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E281" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F281" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G281" s="14">
+        <f>SUM(C281:F281)</f>
+        <v/>
+      </c>
+      <c r="I281" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J281" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K281" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L281" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M281" s="14">
+        <f>SUM(I281:L281)</f>
+        <v/>
+      </c>
+      <c r="O281" s="15">
+        <f>IFERROR(I281/C281-1,"")</f>
+        <v/>
+      </c>
+      <c r="P281" s="15">
+        <f>IFERROR(J281/D281-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q281" s="15">
+        <f>IFERROR(K281/E281-1,"")</f>
+        <v/>
+      </c>
+      <c r="R281" s="15">
+        <f>IFERROR(L281/F281-1,"")</f>
+        <v/>
+      </c>
+      <c r="S281" s="15">
+        <f>IFERROR(M281/G281-1,"")</f>
+        <v/>
+      </c>
+      <c r="U281" s="16" t="n"/>
+      <c r="V281" s="16" t="n"/>
+      <c r="W281" s="16" t="n"/>
+      <c r="X281" s="16">
+        <f>IFERROR(W281-V281,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="282">
+      <c r="B282" s="13" t="inlineStr">
+        <is>
+          <t>20-39</t>
+        </is>
+      </c>
+      <c r="C282" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D282" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E282" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F282" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G282" s="14">
+        <f>SUM(C282:F282)</f>
+        <v/>
+      </c>
+      <c r="I282" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J282" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K282" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L282" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M282" s="14">
+        <f>SUM(I282:L282)</f>
+        <v/>
+      </c>
+      <c r="O282" s="15">
+        <f>IFERROR(I282/C282-1,"")</f>
+        <v/>
+      </c>
+      <c r="P282" s="15">
+        <f>IFERROR(J282/D282-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q282" s="15">
+        <f>IFERROR(K282/E282-1,"")</f>
+        <v/>
+      </c>
+      <c r="R282" s="15">
+        <f>IFERROR(L282/F282-1,"")</f>
+        <v/>
+      </c>
+      <c r="S282" s="15">
+        <f>IFERROR(M282/G282-1,"")</f>
+        <v/>
+      </c>
+      <c r="U282" s="16" t="n"/>
+      <c r="V282" s="16" t="n"/>
+      <c r="W282" s="16" t="n"/>
+      <c r="X282" s="16">
+        <f>IFERROR(W282-V282,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="283">
+      <c r="B283" s="13" t="inlineStr">
+        <is>
+          <t>40-99</t>
+        </is>
+      </c>
+      <c r="C283" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D283" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E283" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F283" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G283" s="14">
+        <f>SUM(C283:F283)</f>
+        <v/>
+      </c>
+      <c r="I283" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J283" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K283" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L283" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M283" s="14">
+        <f>SUM(I283:L283)</f>
+        <v/>
+      </c>
+      <c r="O283" s="15">
+        <f>IFERROR(I283/C283-1,"")</f>
+        <v/>
+      </c>
+      <c r="P283" s="15">
+        <f>IFERROR(J283/D283-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q283" s="15">
+        <f>IFERROR(K283/E283-1,"")</f>
+        <v/>
+      </c>
+      <c r="R283" s="15">
+        <f>IFERROR(L283/F283-1,"")</f>
+        <v/>
+      </c>
+      <c r="S283" s="15">
+        <f>IFERROR(M283/G283-1,"")</f>
+        <v/>
+      </c>
+      <c r="U283" s="16" t="n"/>
+      <c r="V283" s="16" t="n"/>
+      <c r="W283" s="16" t="n"/>
+      <c r="X283" s="16">
+        <f>IFERROR(W283-V283,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="284">
+      <c r="B284" s="13" t="inlineStr">
+        <is>
+          <t>100+</t>
+        </is>
+      </c>
+      <c r="C284" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D284" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E284" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F284" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G284" s="14">
+        <f>SUM(C284:F284)</f>
+        <v/>
+      </c>
+      <c r="I284" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J284" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K284" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L284" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M284" s="14">
+        <f>SUM(I284:L284)</f>
+        <v/>
+      </c>
+      <c r="O284" s="15">
+        <f>IFERROR(I284/C284-1,"")</f>
+        <v/>
+      </c>
+      <c r="P284" s="15">
+        <f>IFERROR(J284/D284-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q284" s="15">
+        <f>IFERROR(K284/E284-1,"")</f>
+        <v/>
+      </c>
+      <c r="R284" s="15">
+        <f>IFERROR(L284/F284-1,"")</f>
+        <v/>
+      </c>
+      <c r="S284" s="15">
+        <f>IFERROR(M284/G284-1,"")</f>
+        <v/>
+      </c>
+      <c r="U284" s="16" t="n"/>
+      <c r="V284" s="16" t="n"/>
+      <c r="W284" s="16" t="n"/>
+      <c r="X284" s="16">
+        <f>IFERROR(W284-V284,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="285">
+      <c r="B285" s="17" t="inlineStr">
+        <is>
+          <t>overall</t>
+        </is>
+      </c>
+      <c r="C285" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D285" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E285" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F285" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G285" s="18">
+        <f>SUM(C285:F285)</f>
+        <v/>
+      </c>
+      <c r="I285" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J285" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K285" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L285" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M285" s="18">
+        <f>SUM(I285:L285)</f>
+        <v/>
+      </c>
+      <c r="O285" s="19">
+        <f>IFERROR(I285/C285-1,"")</f>
+        <v/>
+      </c>
+      <c r="P285" s="19">
+        <f>IFERROR(J285/D285-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q285" s="19">
+        <f>IFERROR(K285/E285-1,"")</f>
+        <v/>
+      </c>
+      <c r="R285" s="19">
+        <f>IFERROR(L285/F285-1,"")</f>
+        <v/>
+      </c>
+      <c r="S285" s="19">
+        <f>IFERROR(M285/G285-1,"")</f>
+        <v/>
+      </c>
+      <c r="U285" s="20" t="n"/>
+      <c r="V285" s="20" t="n"/>
+      <c r="W285" s="20" t="n"/>
+      <c r="X285" s="20">
+        <f>IFERROR(W285-V285,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="288">
+      <c r="B288" s="2" t="inlineStr">
+        <is>
+          <t>◆ 3-star Pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="C289" s="3" t="inlineStr">
+        <is>
+          <t>◄ CURRENT (actuals: data + calc) ►</t>
+        </is>
+      </c>
+      <c r="D289" s="3" t="n"/>
+      <c r="E289" s="3" t="n"/>
+      <c r="F289" s="3" t="n"/>
+      <c r="G289" s="3" t="n"/>
+      <c r="I289" s="4" t="inlineStr">
+        <is>
+          <t>◄ SIMULATED (EcoGainsSim v4) ►</t>
+        </is>
+      </c>
+      <c r="J289" s="4" t="n"/>
+      <c r="K289" s="4" t="n"/>
+      <c r="L289" s="4" t="n"/>
+      <c r="M289" s="4" t="n"/>
+      <c r="O289" s="5" t="inlineStr">
+        <is>
+          <t>Δ</t>
+        </is>
+      </c>
+      <c r="P289" s="5" t="n"/>
+      <c r="Q289" s="5" t="n"/>
+      <c r="R289" s="5" t="n"/>
+      <c r="S289" s="5" t="n"/>
+      <c r="U289" s="6" t="inlineStr">
+        <is>
+          <t>◄ NET / earner (spend held constant) ►</t>
+        </is>
+      </c>
+      <c r="V289" s="6" t="n"/>
+      <c r="W289" s="6" t="n"/>
+      <c r="X289" s="6" t="n"/>
+    </row>
+    <row r="290">
+      <c r="B290" s="7" t="inlineStr">
+        <is>
+          <t>Segment</t>
+        </is>
+      </c>
+      <c r="C290" s="8" t="inlineStr">
+        <is>
+          <t>PAID</t>
+        </is>
+      </c>
+      <c r="D290" s="8" t="inlineStr">
+        <is>
+          <t>ADS</t>
+        </is>
+      </c>
+      <c r="E290" s="8" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="F290" s="8" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="G290" s="8" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="I290" s="9" t="inlineStr">
+        <is>
+          <t>PAID</t>
+        </is>
+      </c>
+      <c r="J290" s="9" t="inlineStr">
+        <is>
+          <t>ADS</t>
+        </is>
+      </c>
+      <c r="K290" s="9" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="L290" s="9" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="M290" s="9" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="O290" s="10" t="inlineStr">
+        <is>
+          <t>PAID</t>
+        </is>
+      </c>
+      <c r="P290" s="10" t="inlineStr">
+        <is>
+          <t>ADS</t>
+        </is>
+      </c>
+      <c r="Q290" s="10" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="R290" s="10" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="S290" s="10" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="U290" s="11" t="inlineStr">
+        <is>
+          <t>cur spend</t>
+        </is>
+      </c>
+      <c r="V290" s="11" t="inlineStr">
+        <is>
+          <t>cur net</t>
+        </is>
+      </c>
+      <c r="W290" s="11" t="inlineStr">
+        <is>
+          <t>new net</t>
+        </is>
+      </c>
+      <c r="X290" s="11" t="inlineStr">
+        <is>
+          <t>net Δ</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="B291" s="12" t="inlineStr">
+        <is>
+          <t>NONPAYER</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="B292" s="13" t="inlineStr">
+        <is>
+          <t>0-9</t>
+        </is>
+      </c>
+      <c r="C292" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D292" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E292" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F292" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G292" s="14">
+        <f>SUM(C292:F292)</f>
+        <v/>
+      </c>
+      <c r="I292" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J292" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K292" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L292" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M292" s="14">
+        <f>SUM(I292:L292)</f>
+        <v/>
+      </c>
+      <c r="O292" s="15">
+        <f>IFERROR(I292/C292-1,"")</f>
+        <v/>
+      </c>
+      <c r="P292" s="15">
+        <f>IFERROR(J292/D292-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q292" s="15">
+        <f>IFERROR(K292/E292-1,"")</f>
+        <v/>
+      </c>
+      <c r="R292" s="15">
+        <f>IFERROR(L292/F292-1,"")</f>
+        <v/>
+      </c>
+      <c r="S292" s="15">
+        <f>IFERROR(M292/G292-1,"")</f>
+        <v/>
+      </c>
+      <c r="U292" s="16" t="n"/>
+      <c r="V292" s="16" t="n"/>
+      <c r="W292" s="16" t="n"/>
+      <c r="X292" s="16">
+        <f>IFERROR(W292-V292,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="293">
+      <c r="B293" s="13" t="inlineStr">
+        <is>
+          <t>10-19</t>
+        </is>
+      </c>
+      <c r="C293" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D293" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E293" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F293" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G293" s="14">
+        <f>SUM(C293:F293)</f>
+        <v/>
+      </c>
+      <c r="I293" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J293" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K293" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L293" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M293" s="14">
+        <f>SUM(I293:L293)</f>
+        <v/>
+      </c>
+      <c r="O293" s="15">
+        <f>IFERROR(I293/C293-1,"")</f>
+        <v/>
+      </c>
+      <c r="P293" s="15">
+        <f>IFERROR(J293/D293-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q293" s="15">
+        <f>IFERROR(K293/E293-1,"")</f>
+        <v/>
+      </c>
+      <c r="R293" s="15">
+        <f>IFERROR(L293/F293-1,"")</f>
+        <v/>
+      </c>
+      <c r="S293" s="15">
+        <f>IFERROR(M293/G293-1,"")</f>
+        <v/>
+      </c>
+      <c r="U293" s="16" t="n"/>
+      <c r="V293" s="16" t="n"/>
+      <c r="W293" s="16" t="n"/>
+      <c r="X293" s="16">
+        <f>IFERROR(W293-V293,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="294">
+      <c r="B294" s="13" t="inlineStr">
+        <is>
+          <t>20-39</t>
+        </is>
+      </c>
+      <c r="C294" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D294" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E294" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F294" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G294" s="14">
+        <f>SUM(C294:F294)</f>
+        <v/>
+      </c>
+      <c r="I294" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J294" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K294" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L294" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M294" s="14">
+        <f>SUM(I294:L294)</f>
+        <v/>
+      </c>
+      <c r="O294" s="15">
+        <f>IFERROR(I294/C294-1,"")</f>
+        <v/>
+      </c>
+      <c r="P294" s="15">
+        <f>IFERROR(J294/D294-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q294" s="15">
+        <f>IFERROR(K294/E294-1,"")</f>
+        <v/>
+      </c>
+      <c r="R294" s="15">
+        <f>IFERROR(L294/F294-1,"")</f>
+        <v/>
+      </c>
+      <c r="S294" s="15">
+        <f>IFERROR(M294/G294-1,"")</f>
+        <v/>
+      </c>
+      <c r="U294" s="16" t="n"/>
+      <c r="V294" s="16" t="n"/>
+      <c r="W294" s="16" t="n"/>
+      <c r="X294" s="16">
+        <f>IFERROR(W294-V294,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="295">
+      <c r="B295" s="13" t="inlineStr">
+        <is>
+          <t>40-99</t>
+        </is>
+      </c>
+      <c r="C295" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D295" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E295" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F295" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G295" s="14">
+        <f>SUM(C295:F295)</f>
+        <v/>
+      </c>
+      <c r="I295" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J295" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K295" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L295" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M295" s="14">
+        <f>SUM(I295:L295)</f>
+        <v/>
+      </c>
+      <c r="O295" s="15">
+        <f>IFERROR(I295/C295-1,"")</f>
+        <v/>
+      </c>
+      <c r="P295" s="15">
+        <f>IFERROR(J295/D295-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q295" s="15">
+        <f>IFERROR(K295/E295-1,"")</f>
+        <v/>
+      </c>
+      <c r="R295" s="15">
+        <f>IFERROR(L295/F295-1,"")</f>
+        <v/>
+      </c>
+      <c r="S295" s="15">
+        <f>IFERROR(M295/G295-1,"")</f>
+        <v/>
+      </c>
+      <c r="U295" s="16" t="n"/>
+      <c r="V295" s="16" t="n"/>
+      <c r="W295" s="16" t="n"/>
+      <c r="X295" s="16">
+        <f>IFERROR(W295-V295,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="296">
+      <c r="B296" s="13" t="inlineStr">
+        <is>
+          <t>100+</t>
+        </is>
+      </c>
+      <c r="C296" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D296" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E296" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F296" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G296" s="14">
+        <f>SUM(C296:F296)</f>
+        <v/>
+      </c>
+      <c r="I296" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J296" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K296" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L296" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M296" s="14">
+        <f>SUM(I296:L296)</f>
+        <v/>
+      </c>
+      <c r="O296" s="15">
+        <f>IFERROR(I296/C296-1,"")</f>
+        <v/>
+      </c>
+      <c r="P296" s="15">
+        <f>IFERROR(J296/D296-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q296" s="15">
+        <f>IFERROR(K296/E296-1,"")</f>
+        <v/>
+      </c>
+      <c r="R296" s="15">
+        <f>IFERROR(L296/F296-1,"")</f>
+        <v/>
+      </c>
+      <c r="S296" s="15">
+        <f>IFERROR(M296/G296-1,"")</f>
+        <v/>
+      </c>
+      <c r="U296" s="16" t="n"/>
+      <c r="V296" s="16" t="n"/>
+      <c r="W296" s="16" t="n"/>
+      <c r="X296" s="16">
+        <f>IFERROR(W296-V296,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="297">
+      <c r="B297" s="17" t="inlineStr">
+        <is>
+          <t>overall</t>
+        </is>
+      </c>
+      <c r="C297" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D297" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E297" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F297" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G297" s="18">
+        <f>SUM(C297:F297)</f>
+        <v/>
+      </c>
+      <c r="I297" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J297" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K297" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L297" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M297" s="18">
+        <f>SUM(I297:L297)</f>
+        <v/>
+      </c>
+      <c r="O297" s="19">
+        <f>IFERROR(I297/C297-1,"")</f>
+        <v/>
+      </c>
+      <c r="P297" s="19">
+        <f>IFERROR(J297/D297-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q297" s="19">
+        <f>IFERROR(K297/E297-1,"")</f>
+        <v/>
+      </c>
+      <c r="R297" s="19">
+        <f>IFERROR(L297/F297-1,"")</f>
+        <v/>
+      </c>
+      <c r="S297" s="19">
+        <f>IFERROR(M297/G297-1,"")</f>
+        <v/>
+      </c>
+      <c r="U297" s="20" t="n"/>
+      <c r="V297" s="20" t="n"/>
+      <c r="W297" s="20" t="n"/>
+      <c r="X297" s="20">
+        <f>IFERROR(W297-V297,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="298">
+      <c r="B298" s="12" t="inlineStr">
+        <is>
+          <t>PAYER</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="B299" s="13" t="inlineStr">
+        <is>
+          <t>0-9</t>
+        </is>
+      </c>
+      <c r="C299" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D299" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E299" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F299" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G299" s="14">
+        <f>SUM(C299:F299)</f>
+        <v/>
+      </c>
+      <c r="I299" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J299" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K299" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L299" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M299" s="14">
+        <f>SUM(I299:L299)</f>
+        <v/>
+      </c>
+      <c r="O299" s="15">
+        <f>IFERROR(I299/C299-1,"")</f>
+        <v/>
+      </c>
+      <c r="P299" s="15">
+        <f>IFERROR(J299/D299-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q299" s="15">
+        <f>IFERROR(K299/E299-1,"")</f>
+        <v/>
+      </c>
+      <c r="R299" s="15">
+        <f>IFERROR(L299/F299-1,"")</f>
+        <v/>
+      </c>
+      <c r="S299" s="15">
+        <f>IFERROR(M299/G299-1,"")</f>
+        <v/>
+      </c>
+      <c r="U299" s="16" t="n"/>
+      <c r="V299" s="16" t="n"/>
+      <c r="W299" s="16" t="n"/>
+      <c r="X299" s="16">
+        <f>IFERROR(W299-V299,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="300">
+      <c r="B300" s="13" t="inlineStr">
+        <is>
+          <t>10-19</t>
+        </is>
+      </c>
+      <c r="C300" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D300" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E300" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F300" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G300" s="14">
+        <f>SUM(C300:F300)</f>
+        <v/>
+      </c>
+      <c r="I300" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J300" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K300" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L300" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M300" s="14">
+        <f>SUM(I300:L300)</f>
+        <v/>
+      </c>
+      <c r="O300" s="15">
+        <f>IFERROR(I300/C300-1,"")</f>
+        <v/>
+      </c>
+      <c r="P300" s="15">
+        <f>IFERROR(J300/D300-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q300" s="15">
+        <f>IFERROR(K300/E300-1,"")</f>
+        <v/>
+      </c>
+      <c r="R300" s="15">
+        <f>IFERROR(L300/F300-1,"")</f>
+        <v/>
+      </c>
+      <c r="S300" s="15">
+        <f>IFERROR(M300/G300-1,"")</f>
+        <v/>
+      </c>
+      <c r="U300" s="16" t="n"/>
+      <c r="V300" s="16" t="n"/>
+      <c r="W300" s="16" t="n"/>
+      <c r="X300" s="16">
+        <f>IFERROR(W300-V300,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="301">
+      <c r="B301" s="13" t="inlineStr">
+        <is>
+          <t>20-39</t>
+        </is>
+      </c>
+      <c r="C301" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D301" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E301" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F301" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G301" s="14">
+        <f>SUM(C301:F301)</f>
+        <v/>
+      </c>
+      <c r="I301" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J301" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K301" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L301" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M301" s="14">
+        <f>SUM(I301:L301)</f>
+        <v/>
+      </c>
+      <c r="O301" s="15">
+        <f>IFERROR(I301/C301-1,"")</f>
+        <v/>
+      </c>
+      <c r="P301" s="15">
+        <f>IFERROR(J301/D301-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q301" s="15">
+        <f>IFERROR(K301/E301-1,"")</f>
+        <v/>
+      </c>
+      <c r="R301" s="15">
+        <f>IFERROR(L301/F301-1,"")</f>
+        <v/>
+      </c>
+      <c r="S301" s="15">
+        <f>IFERROR(M301/G301-1,"")</f>
+        <v/>
+      </c>
+      <c r="U301" s="16" t="n"/>
+      <c r="V301" s="16" t="n"/>
+      <c r="W301" s="16" t="n"/>
+      <c r="X301" s="16">
+        <f>IFERROR(W301-V301,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="302">
+      <c r="B302" s="13" t="inlineStr">
+        <is>
+          <t>40-99</t>
+        </is>
+      </c>
+      <c r="C302" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D302" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E302" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F302" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G302" s="14">
+        <f>SUM(C302:F302)</f>
+        <v/>
+      </c>
+      <c r="I302" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J302" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K302" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L302" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M302" s="14">
+        <f>SUM(I302:L302)</f>
+        <v/>
+      </c>
+      <c r="O302" s="15">
+        <f>IFERROR(I302/C302-1,"")</f>
+        <v/>
+      </c>
+      <c r="P302" s="15">
+        <f>IFERROR(J302/D302-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q302" s="15">
+        <f>IFERROR(K302/E302-1,"")</f>
+        <v/>
+      </c>
+      <c r="R302" s="15">
+        <f>IFERROR(L302/F302-1,"")</f>
+        <v/>
+      </c>
+      <c r="S302" s="15">
+        <f>IFERROR(M302/G302-1,"")</f>
+        <v/>
+      </c>
+      <c r="U302" s="16" t="n"/>
+      <c r="V302" s="16" t="n"/>
+      <c r="W302" s="16" t="n"/>
+      <c r="X302" s="16">
+        <f>IFERROR(W302-V302,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="303">
+      <c r="B303" s="13" t="inlineStr">
+        <is>
+          <t>100+</t>
+        </is>
+      </c>
+      <c r="C303" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D303" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E303" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F303" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G303" s="14">
+        <f>SUM(C303:F303)</f>
+        <v/>
+      </c>
+      <c r="I303" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J303" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K303" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L303" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M303" s="14">
+        <f>SUM(I303:L303)</f>
+        <v/>
+      </c>
+      <c r="O303" s="15">
+        <f>IFERROR(I303/C303-1,"")</f>
+        <v/>
+      </c>
+      <c r="P303" s="15">
+        <f>IFERROR(J303/D303-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q303" s="15">
+        <f>IFERROR(K303/E303-1,"")</f>
+        <v/>
+      </c>
+      <c r="R303" s="15">
+        <f>IFERROR(L303/F303-1,"")</f>
+        <v/>
+      </c>
+      <c r="S303" s="15">
+        <f>IFERROR(M303/G303-1,"")</f>
+        <v/>
+      </c>
+      <c r="U303" s="16" t="n"/>
+      <c r="V303" s="16" t="n"/>
+      <c r="W303" s="16" t="n"/>
+      <c r="X303" s="16">
+        <f>IFERROR(W303-V303,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="304">
+      <c r="B304" s="17" t="inlineStr">
+        <is>
+          <t>overall</t>
+        </is>
+      </c>
+      <c r="C304" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D304" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E304" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F304" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G304" s="18">
+        <f>SUM(C304:F304)</f>
+        <v/>
+      </c>
+      <c r="I304" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J304" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K304" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L304" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M304" s="18">
+        <f>SUM(I304:L304)</f>
+        <v/>
+      </c>
+      <c r="O304" s="19">
+        <f>IFERROR(I304/C304-1,"")</f>
+        <v/>
+      </c>
+      <c r="P304" s="19">
+        <f>IFERROR(J304/D304-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q304" s="19">
+        <f>IFERROR(K304/E304-1,"")</f>
+        <v/>
+      </c>
+      <c r="R304" s="19">
+        <f>IFERROR(L304/F304-1,"")</f>
+        <v/>
+      </c>
+      <c r="S304" s="19">
+        <f>IFERROR(M304/G304-1,"")</f>
+        <v/>
+      </c>
+      <c r="U304" s="20" t="n"/>
+      <c r="V304" s="20" t="n"/>
+      <c r="W304" s="20" t="n"/>
+      <c r="X304" s="20">
+        <f>IFERROR(W304-V304,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="307">
+      <c r="B307" s="2" t="inlineStr">
+        <is>
+          <t>◆ 4-star Pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="C308" s="3" t="inlineStr">
+        <is>
+          <t>◄ CURRENT (actuals: data + calc) ►</t>
+        </is>
+      </c>
+      <c r="D308" s="3" t="n"/>
+      <c r="E308" s="3" t="n"/>
+      <c r="F308" s="3" t="n"/>
+      <c r="G308" s="3" t="n"/>
+      <c r="I308" s="4" t="inlineStr">
+        <is>
+          <t>◄ SIMULATED (EcoGainsSim v4) ►</t>
+        </is>
+      </c>
+      <c r="J308" s="4" t="n"/>
+      <c r="K308" s="4" t="n"/>
+      <c r="L308" s="4" t="n"/>
+      <c r="M308" s="4" t="n"/>
+      <c r="O308" s="5" t="inlineStr">
+        <is>
+          <t>Δ</t>
+        </is>
+      </c>
+      <c r="P308" s="5" t="n"/>
+      <c r="Q308" s="5" t="n"/>
+      <c r="R308" s="5" t="n"/>
+      <c r="S308" s="5" t="n"/>
+      <c r="U308" s="6" t="inlineStr">
+        <is>
+          <t>◄ NET / earner (spend held constant) ►</t>
+        </is>
+      </c>
+      <c r="V308" s="6" t="n"/>
+      <c r="W308" s="6" t="n"/>
+      <c r="X308" s="6" t="n"/>
+    </row>
+    <row r="309">
+      <c r="B309" s="7" t="inlineStr">
+        <is>
+          <t>Segment</t>
+        </is>
+      </c>
+      <c r="C309" s="8" t="inlineStr">
+        <is>
+          <t>PAID</t>
+        </is>
+      </c>
+      <c r="D309" s="8" t="inlineStr">
+        <is>
+          <t>ADS</t>
+        </is>
+      </c>
+      <c r="E309" s="8" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="F309" s="8" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="G309" s="8" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="I309" s="9" t="inlineStr">
+        <is>
+          <t>PAID</t>
+        </is>
+      </c>
+      <c r="J309" s="9" t="inlineStr">
+        <is>
+          <t>ADS</t>
+        </is>
+      </c>
+      <c r="K309" s="9" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="L309" s="9" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="M309" s="9" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="O309" s="10" t="inlineStr">
+        <is>
+          <t>PAID</t>
+        </is>
+      </c>
+      <c r="P309" s="10" t="inlineStr">
+        <is>
+          <t>ADS</t>
+        </is>
+      </c>
+      <c r="Q309" s="10" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="R309" s="10" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="S309" s="10" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="U309" s="11" t="inlineStr">
+        <is>
+          <t>cur spend</t>
+        </is>
+      </c>
+      <c r="V309" s="11" t="inlineStr">
+        <is>
+          <t>cur net</t>
+        </is>
+      </c>
+      <c r="W309" s="11" t="inlineStr">
+        <is>
+          <t>new net</t>
+        </is>
+      </c>
+      <c r="X309" s="11" t="inlineStr">
+        <is>
+          <t>net Δ</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="B310" s="12" t="inlineStr">
+        <is>
+          <t>NONPAYER</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="B311" s="13" t="inlineStr">
+        <is>
+          <t>0-9</t>
+        </is>
+      </c>
+      <c r="C311" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D311" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E311" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F311" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G311" s="14">
+        <f>SUM(C311:F311)</f>
+        <v/>
+      </c>
+      <c r="I311" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J311" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K311" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L311" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M311" s="14">
+        <f>SUM(I311:L311)</f>
+        <v/>
+      </c>
+      <c r="O311" s="15">
+        <f>IFERROR(I311/C311-1,"")</f>
+        <v/>
+      </c>
+      <c r="P311" s="15">
+        <f>IFERROR(J311/D311-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q311" s="15">
+        <f>IFERROR(K311/E311-1,"")</f>
+        <v/>
+      </c>
+      <c r="R311" s="15">
+        <f>IFERROR(L311/F311-1,"")</f>
+        <v/>
+      </c>
+      <c r="S311" s="15">
+        <f>IFERROR(M311/G311-1,"")</f>
+        <v/>
+      </c>
+      <c r="U311" s="16" t="n"/>
+      <c r="V311" s="16" t="n"/>
+      <c r="W311" s="16" t="n"/>
+      <c r="X311" s="16">
+        <f>IFERROR(W311-V311,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="312">
+      <c r="B312" s="13" t="inlineStr">
+        <is>
+          <t>10-19</t>
+        </is>
+      </c>
+      <c r="C312" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D312" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E312" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F312" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G312" s="14">
+        <f>SUM(C312:F312)</f>
+        <v/>
+      </c>
+      <c r="I312" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J312" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K312" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L312" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M312" s="14">
+        <f>SUM(I312:L312)</f>
+        <v/>
+      </c>
+      <c r="O312" s="15">
+        <f>IFERROR(I312/C312-1,"")</f>
+        <v/>
+      </c>
+      <c r="P312" s="15">
+        <f>IFERROR(J312/D312-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q312" s="15">
+        <f>IFERROR(K312/E312-1,"")</f>
+        <v/>
+      </c>
+      <c r="R312" s="15">
+        <f>IFERROR(L312/F312-1,"")</f>
+        <v/>
+      </c>
+      <c r="S312" s="15">
+        <f>IFERROR(M312/G312-1,"")</f>
+        <v/>
+      </c>
+      <c r="U312" s="16" t="n"/>
+      <c r="V312" s="16" t="n"/>
+      <c r="W312" s="16" t="n"/>
+      <c r="X312" s="16">
+        <f>IFERROR(W312-V312,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="313">
+      <c r="B313" s="13" t="inlineStr">
+        <is>
+          <t>20-39</t>
+        </is>
+      </c>
+      <c r="C313" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D313" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E313" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F313" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G313" s="14">
+        <f>SUM(C313:F313)</f>
+        <v/>
+      </c>
+      <c r="I313" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J313" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K313" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L313" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M313" s="14">
+        <f>SUM(I313:L313)</f>
+        <v/>
+      </c>
+      <c r="O313" s="15">
+        <f>IFERROR(I313/C313-1,"")</f>
+        <v/>
+      </c>
+      <c r="P313" s="15">
+        <f>IFERROR(J313/D313-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q313" s="15">
+        <f>IFERROR(K313/E313-1,"")</f>
+        <v/>
+      </c>
+      <c r="R313" s="15">
+        <f>IFERROR(L313/F313-1,"")</f>
+        <v/>
+      </c>
+      <c r="S313" s="15">
+        <f>IFERROR(M313/G313-1,"")</f>
+        <v/>
+      </c>
+      <c r="U313" s="16" t="n"/>
+      <c r="V313" s="16" t="n"/>
+      <c r="W313" s="16" t="n"/>
+      <c r="X313" s="16">
+        <f>IFERROR(W313-V313,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="314">
+      <c r="B314" s="13" t="inlineStr">
+        <is>
+          <t>40-99</t>
+        </is>
+      </c>
+      <c r="C314" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D314" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E314" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F314" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G314" s="14">
+        <f>SUM(C314:F314)</f>
+        <v/>
+      </c>
+      <c r="I314" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J314" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K314" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L314" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M314" s="14">
+        <f>SUM(I314:L314)</f>
+        <v/>
+      </c>
+      <c r="O314" s="15">
+        <f>IFERROR(I314/C314-1,"")</f>
+        <v/>
+      </c>
+      <c r="P314" s="15">
+        <f>IFERROR(J314/D314-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q314" s="15">
+        <f>IFERROR(K314/E314-1,"")</f>
+        <v/>
+      </c>
+      <c r="R314" s="15">
+        <f>IFERROR(L314/F314-1,"")</f>
+        <v/>
+      </c>
+      <c r="S314" s="15">
+        <f>IFERROR(M314/G314-1,"")</f>
+        <v/>
+      </c>
+      <c r="U314" s="16" t="n"/>
+      <c r="V314" s="16" t="n"/>
+      <c r="W314" s="16" t="n"/>
+      <c r="X314" s="16">
+        <f>IFERROR(W314-V314,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="315">
+      <c r="B315" s="13" t="inlineStr">
+        <is>
+          <t>100+</t>
+        </is>
+      </c>
+      <c r="C315" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D315" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E315" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F315" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G315" s="14">
+        <f>SUM(C315:F315)</f>
+        <v/>
+      </c>
+      <c r="I315" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J315" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K315" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L315" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M315" s="14">
+        <f>SUM(I315:L315)</f>
+        <v/>
+      </c>
+      <c r="O315" s="15">
+        <f>IFERROR(I315/C315-1,"")</f>
+        <v/>
+      </c>
+      <c r="P315" s="15">
+        <f>IFERROR(J315/D315-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q315" s="15">
+        <f>IFERROR(K315/E315-1,"")</f>
+        <v/>
+      </c>
+      <c r="R315" s="15">
+        <f>IFERROR(L315/F315-1,"")</f>
+        <v/>
+      </c>
+      <c r="S315" s="15">
+        <f>IFERROR(M315/G315-1,"")</f>
+        <v/>
+      </c>
+      <c r="U315" s="16" t="n"/>
+      <c r="V315" s="16" t="n"/>
+      <c r="W315" s="16" t="n"/>
+      <c r="X315" s="16">
+        <f>IFERROR(W315-V315,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="316">
+      <c r="B316" s="17" t="inlineStr">
+        <is>
+          <t>overall</t>
+        </is>
+      </c>
+      <c r="C316" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D316" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E316" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F316" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G316" s="18">
+        <f>SUM(C316:F316)</f>
+        <v/>
+      </c>
+      <c r="I316" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J316" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K316" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L316" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M316" s="18">
+        <f>SUM(I316:L316)</f>
+        <v/>
+      </c>
+      <c r="O316" s="19">
+        <f>IFERROR(I316/C316-1,"")</f>
+        <v/>
+      </c>
+      <c r="P316" s="19">
+        <f>IFERROR(J316/D316-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q316" s="19">
+        <f>IFERROR(K316/E316-1,"")</f>
+        <v/>
+      </c>
+      <c r="R316" s="19">
+        <f>IFERROR(L316/F316-1,"")</f>
+        <v/>
+      </c>
+      <c r="S316" s="19">
+        <f>IFERROR(M316/G316-1,"")</f>
+        <v/>
+      </c>
+      <c r="U316" s="20" t="n"/>
+      <c r="V316" s="20" t="n"/>
+      <c r="W316" s="20" t="n"/>
+      <c r="X316" s="20">
+        <f>IFERROR(W316-V316,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="317">
+      <c r="B317" s="12" t="inlineStr">
+        <is>
+          <t>PAYER</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="B318" s="13" t="inlineStr">
+        <is>
+          <t>0-9</t>
+        </is>
+      </c>
+      <c r="C318" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D318" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E318" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F318" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G318" s="14">
+        <f>SUM(C318:F318)</f>
+        <v/>
+      </c>
+      <c r="I318" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J318" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K318" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L318" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M318" s="14">
+        <f>SUM(I318:L318)</f>
+        <v/>
+      </c>
+      <c r="O318" s="15">
+        <f>IFERROR(I318/C318-1,"")</f>
+        <v/>
+      </c>
+      <c r="P318" s="15">
+        <f>IFERROR(J318/D318-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q318" s="15">
+        <f>IFERROR(K318/E318-1,"")</f>
+        <v/>
+      </c>
+      <c r="R318" s="15">
+        <f>IFERROR(L318/F318-1,"")</f>
+        <v/>
+      </c>
+      <c r="S318" s="15">
+        <f>IFERROR(M318/G318-1,"")</f>
+        <v/>
+      </c>
+      <c r="U318" s="16" t="n"/>
+      <c r="V318" s="16" t="n"/>
+      <c r="W318" s="16" t="n"/>
+      <c r="X318" s="16">
+        <f>IFERROR(W318-V318,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="319">
+      <c r="B319" s="13" t="inlineStr">
+        <is>
+          <t>10-19</t>
+        </is>
+      </c>
+      <c r="C319" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D319" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E319" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F319" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G319" s="14">
+        <f>SUM(C319:F319)</f>
+        <v/>
+      </c>
+      <c r="I319" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J319" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K319" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L319" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M319" s="14">
+        <f>SUM(I319:L319)</f>
+        <v/>
+      </c>
+      <c r="O319" s="15">
+        <f>IFERROR(I319/C319-1,"")</f>
+        <v/>
+      </c>
+      <c r="P319" s="15">
+        <f>IFERROR(J319/D319-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q319" s="15">
+        <f>IFERROR(K319/E319-1,"")</f>
+        <v/>
+      </c>
+      <c r="R319" s="15">
+        <f>IFERROR(L319/F319-1,"")</f>
+        <v/>
+      </c>
+      <c r="S319" s="15">
+        <f>IFERROR(M319/G319-1,"")</f>
+        <v/>
+      </c>
+      <c r="U319" s="16" t="n"/>
+      <c r="V319" s="16" t="n"/>
+      <c r="W319" s="16" t="n"/>
+      <c r="X319" s="16">
+        <f>IFERROR(W319-V319,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="320">
+      <c r="B320" s="13" t="inlineStr">
+        <is>
+          <t>20-39</t>
+        </is>
+      </c>
+      <c r="C320" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D320" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E320" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F320" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G320" s="14">
+        <f>SUM(C320:F320)</f>
+        <v/>
+      </c>
+      <c r="I320" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J320" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K320" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L320" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M320" s="14">
+        <f>SUM(I320:L320)</f>
+        <v/>
+      </c>
+      <c r="O320" s="15">
+        <f>IFERROR(I320/C320-1,"")</f>
+        <v/>
+      </c>
+      <c r="P320" s="15">
+        <f>IFERROR(J320/D320-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q320" s="15">
+        <f>IFERROR(K320/E320-1,"")</f>
+        <v/>
+      </c>
+      <c r="R320" s="15">
+        <f>IFERROR(L320/F320-1,"")</f>
+        <v/>
+      </c>
+      <c r="S320" s="15">
+        <f>IFERROR(M320/G320-1,"")</f>
+        <v/>
+      </c>
+      <c r="U320" s="16" t="n"/>
+      <c r="V320" s="16" t="n"/>
+      <c r="W320" s="16" t="n"/>
+      <c r="X320" s="16">
+        <f>IFERROR(W320-V320,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="321">
+      <c r="B321" s="13" t="inlineStr">
+        <is>
+          <t>40-99</t>
+        </is>
+      </c>
+      <c r="C321" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D321" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E321" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F321" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G321" s="14">
+        <f>SUM(C321:F321)</f>
+        <v/>
+      </c>
+      <c r="I321" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J321" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K321" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L321" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M321" s="14">
+        <f>SUM(I321:L321)</f>
+        <v/>
+      </c>
+      <c r="O321" s="15">
+        <f>IFERROR(I321/C321-1,"")</f>
+        <v/>
+      </c>
+      <c r="P321" s="15">
+        <f>IFERROR(J321/D321-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q321" s="15">
+        <f>IFERROR(K321/E321-1,"")</f>
+        <v/>
+      </c>
+      <c r="R321" s="15">
+        <f>IFERROR(L321/F321-1,"")</f>
+        <v/>
+      </c>
+      <c r="S321" s="15">
+        <f>IFERROR(M321/G321-1,"")</f>
+        <v/>
+      </c>
+      <c r="U321" s="16" t="n"/>
+      <c r="V321" s="16" t="n"/>
+      <c r="W321" s="16" t="n"/>
+      <c r="X321" s="16">
+        <f>IFERROR(W321-V321,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="322">
+      <c r="B322" s="13" t="inlineStr">
+        <is>
+          <t>100+</t>
+        </is>
+      </c>
+      <c r="C322" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D322" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E322" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F322" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G322" s="14">
+        <f>SUM(C322:F322)</f>
+        <v/>
+      </c>
+      <c r="I322" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J322" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K322" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L322" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M322" s="14">
+        <f>SUM(I322:L322)</f>
+        <v/>
+      </c>
+      <c r="O322" s="15">
+        <f>IFERROR(I322/C322-1,"")</f>
+        <v/>
+      </c>
+      <c r="P322" s="15">
+        <f>IFERROR(J322/D322-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q322" s="15">
+        <f>IFERROR(K322/E322-1,"")</f>
+        <v/>
+      </c>
+      <c r="R322" s="15">
+        <f>IFERROR(L322/F322-1,"")</f>
+        <v/>
+      </c>
+      <c r="S322" s="15">
+        <f>IFERROR(M322/G322-1,"")</f>
+        <v/>
+      </c>
+      <c r="U322" s="16" t="n"/>
+      <c r="V322" s="16" t="n"/>
+      <c r="W322" s="16" t="n"/>
+      <c r="X322" s="16">
+        <f>IFERROR(W322-V322,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="323">
+      <c r="B323" s="17" t="inlineStr">
+        <is>
+          <t>overall</t>
+        </is>
+      </c>
+      <c r="C323" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D323" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E323" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F323" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G323" s="18">
+        <f>SUM(C323:F323)</f>
+        <v/>
+      </c>
+      <c r="I323" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J323" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K323" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L323" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M323" s="18">
+        <f>SUM(I323:L323)</f>
+        <v/>
+      </c>
+      <c r="O323" s="19">
+        <f>IFERROR(I323/C323-1,"")</f>
+        <v/>
+      </c>
+      <c r="P323" s="19">
+        <f>IFERROR(J323/D323-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q323" s="19">
+        <f>IFERROR(K323/E323-1,"")</f>
+        <v/>
+      </c>
+      <c r="R323" s="19">
+        <f>IFERROR(L323/F323-1,"")</f>
+        <v/>
+      </c>
+      <c r="S323" s="19">
+        <f>IFERROR(M323/G323-1,"")</f>
+        <v/>
+      </c>
+      <c r="U323" s="20" t="n"/>
+      <c r="V323" s="20" t="n"/>
+      <c r="W323" s="20" t="n"/>
+      <c r="X323" s="20">
+        <f>IFERROR(W323-V323,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="326">
+      <c r="B326" s="2" t="inlineStr">
+        <is>
+          <t>◆ 5-star Pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="C327" s="3" t="inlineStr">
+        <is>
+          <t>◄ CURRENT (actuals: data + calc) ►</t>
+        </is>
+      </c>
+      <c r="D327" s="3" t="n"/>
+      <c r="E327" s="3" t="n"/>
+      <c r="F327" s="3" t="n"/>
+      <c r="G327" s="3" t="n"/>
+      <c r="I327" s="4" t="inlineStr">
+        <is>
+          <t>◄ SIMULATED (EcoGainsSim v4) ►</t>
+        </is>
+      </c>
+      <c r="J327" s="4" t="n"/>
+      <c r="K327" s="4" t="n"/>
+      <c r="L327" s="4" t="n"/>
+      <c r="M327" s="4" t="n"/>
+      <c r="O327" s="5" t="inlineStr">
+        <is>
+          <t>Δ</t>
+        </is>
+      </c>
+      <c r="P327" s="5" t="n"/>
+      <c r="Q327" s="5" t="n"/>
+      <c r="R327" s="5" t="n"/>
+      <c r="S327" s="5" t="n"/>
+      <c r="U327" s="6" t="inlineStr">
+        <is>
+          <t>◄ NET / earner (spend held constant) ►</t>
+        </is>
+      </c>
+      <c r="V327" s="6" t="n"/>
+      <c r="W327" s="6" t="n"/>
+      <c r="X327" s="6" t="n"/>
+    </row>
+    <row r="328">
+      <c r="B328" s="7" t="inlineStr">
+        <is>
+          <t>Segment</t>
+        </is>
+      </c>
+      <c r="C328" s="8" t="inlineStr">
+        <is>
+          <t>PAID</t>
+        </is>
+      </c>
+      <c r="D328" s="8" t="inlineStr">
+        <is>
+          <t>ADS</t>
+        </is>
+      </c>
+      <c r="E328" s="8" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="F328" s="8" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="G328" s="8" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="I328" s="9" t="inlineStr">
+        <is>
+          <t>PAID</t>
+        </is>
+      </c>
+      <c r="J328" s="9" t="inlineStr">
+        <is>
+          <t>ADS</t>
+        </is>
+      </c>
+      <c r="K328" s="9" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="L328" s="9" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="M328" s="9" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="O328" s="10" t="inlineStr">
+        <is>
+          <t>PAID</t>
+        </is>
+      </c>
+      <c r="P328" s="10" t="inlineStr">
+        <is>
+          <t>ADS</t>
+        </is>
+      </c>
+      <c r="Q328" s="10" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="R328" s="10" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="S328" s="10" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="U328" s="11" t="inlineStr">
+        <is>
+          <t>cur spend</t>
+        </is>
+      </c>
+      <c r="V328" s="11" t="inlineStr">
+        <is>
+          <t>cur net</t>
+        </is>
+      </c>
+      <c r="W328" s="11" t="inlineStr">
+        <is>
+          <t>new net</t>
+        </is>
+      </c>
+      <c r="X328" s="11" t="inlineStr">
+        <is>
+          <t>net Δ</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="B329" s="12" t="inlineStr">
+        <is>
+          <t>NONPAYER</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="B330" s="13" t="inlineStr">
+        <is>
+          <t>0-9</t>
+        </is>
+      </c>
+      <c r="C330" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D330" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E330" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F330" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G330" s="14">
+        <f>SUM(C330:F330)</f>
+        <v/>
+      </c>
+      <c r="I330" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J330" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K330" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L330" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M330" s="14">
+        <f>SUM(I330:L330)</f>
+        <v/>
+      </c>
+      <c r="O330" s="15">
+        <f>IFERROR(I330/C330-1,"")</f>
+        <v/>
+      </c>
+      <c r="P330" s="15">
+        <f>IFERROR(J330/D330-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q330" s="15">
+        <f>IFERROR(K330/E330-1,"")</f>
+        <v/>
+      </c>
+      <c r="R330" s="15">
+        <f>IFERROR(L330/F330-1,"")</f>
+        <v/>
+      </c>
+      <c r="S330" s="15">
+        <f>IFERROR(M330/G330-1,"")</f>
+        <v/>
+      </c>
+      <c r="U330" s="16" t="n"/>
+      <c r="V330" s="16" t="n"/>
+      <c r="W330" s="16" t="n"/>
+      <c r="X330" s="16">
+        <f>IFERROR(W330-V330,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="331">
+      <c r="B331" s="13" t="inlineStr">
+        <is>
+          <t>10-19</t>
+        </is>
+      </c>
+      <c r="C331" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D331" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E331" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F331" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G331" s="14">
+        <f>SUM(C331:F331)</f>
+        <v/>
+      </c>
+      <c r="I331" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J331" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K331" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L331" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M331" s="14">
+        <f>SUM(I331:L331)</f>
+        <v/>
+      </c>
+      <c r="O331" s="15">
+        <f>IFERROR(I331/C331-1,"")</f>
+        <v/>
+      </c>
+      <c r="P331" s="15">
+        <f>IFERROR(J331/D331-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q331" s="15">
+        <f>IFERROR(K331/E331-1,"")</f>
+        <v/>
+      </c>
+      <c r="R331" s="15">
+        <f>IFERROR(L331/F331-1,"")</f>
+        <v/>
+      </c>
+      <c r="S331" s="15">
+        <f>IFERROR(M331/G331-1,"")</f>
+        <v/>
+      </c>
+      <c r="U331" s="16" t="n"/>
+      <c r="V331" s="16" t="n"/>
+      <c r="W331" s="16" t="n"/>
+      <c r="X331" s="16">
+        <f>IFERROR(W331-V331,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="332">
+      <c r="B332" s="13" t="inlineStr">
+        <is>
+          <t>20-39</t>
+        </is>
+      </c>
+      <c r="C332" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D332" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E332" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F332" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G332" s="14">
+        <f>SUM(C332:F332)</f>
+        <v/>
+      </c>
+      <c r="I332" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J332" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K332" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L332" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M332" s="14">
+        <f>SUM(I332:L332)</f>
+        <v/>
+      </c>
+      <c r="O332" s="15">
+        <f>IFERROR(I332/C332-1,"")</f>
+        <v/>
+      </c>
+      <c r="P332" s="15">
+        <f>IFERROR(J332/D332-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q332" s="15">
+        <f>IFERROR(K332/E332-1,"")</f>
+        <v/>
+      </c>
+      <c r="R332" s="15">
+        <f>IFERROR(L332/F332-1,"")</f>
+        <v/>
+      </c>
+      <c r="S332" s="15">
+        <f>IFERROR(M332/G332-1,"")</f>
+        <v/>
+      </c>
+      <c r="U332" s="16" t="n"/>
+      <c r="V332" s="16" t="n"/>
+      <c r="W332" s="16" t="n"/>
+      <c r="X332" s="16">
+        <f>IFERROR(W332-V332,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="333">
+      <c r="B333" s="13" t="inlineStr">
+        <is>
+          <t>40-99</t>
+        </is>
+      </c>
+      <c r="C333" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D333" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E333" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F333" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G333" s="14">
+        <f>SUM(C333:F333)</f>
+        <v/>
+      </c>
+      <c r="I333" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J333" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K333" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L333" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M333" s="14">
+        <f>SUM(I333:L333)</f>
+        <v/>
+      </c>
+      <c r="O333" s="15">
+        <f>IFERROR(I333/C333-1,"")</f>
+        <v/>
+      </c>
+      <c r="P333" s="15">
+        <f>IFERROR(J333/D333-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q333" s="15">
+        <f>IFERROR(K333/E333-1,"")</f>
+        <v/>
+      </c>
+      <c r="R333" s="15">
+        <f>IFERROR(L333/F333-1,"")</f>
+        <v/>
+      </c>
+      <c r="S333" s="15">
+        <f>IFERROR(M333/G333-1,"")</f>
+        <v/>
+      </c>
+      <c r="U333" s="16" t="n"/>
+      <c r="V333" s="16" t="n"/>
+      <c r="W333" s="16" t="n"/>
+      <c r="X333" s="16">
+        <f>IFERROR(W333-V333,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="334">
+      <c r="B334" s="13" t="inlineStr">
+        <is>
+          <t>100+</t>
+        </is>
+      </c>
+      <c r="C334" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D334" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E334" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F334" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G334" s="14">
+        <f>SUM(C334:F334)</f>
+        <v/>
+      </c>
+      <c r="I334" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J334" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K334" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L334" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M334" s="14">
+        <f>SUM(I334:L334)</f>
+        <v/>
+      </c>
+      <c r="O334" s="15">
+        <f>IFERROR(I334/C334-1,"")</f>
+        <v/>
+      </c>
+      <c r="P334" s="15">
+        <f>IFERROR(J334/D334-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q334" s="15">
+        <f>IFERROR(K334/E334-1,"")</f>
+        <v/>
+      </c>
+      <c r="R334" s="15">
+        <f>IFERROR(L334/F334-1,"")</f>
+        <v/>
+      </c>
+      <c r="S334" s="15">
+        <f>IFERROR(M334/G334-1,"")</f>
+        <v/>
+      </c>
+      <c r="U334" s="16" t="n"/>
+      <c r="V334" s="16" t="n"/>
+      <c r="W334" s="16" t="n"/>
+      <c r="X334" s="16">
+        <f>IFERROR(W334-V334,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="335">
+      <c r="B335" s="17" t="inlineStr">
+        <is>
+          <t>overall</t>
+        </is>
+      </c>
+      <c r="C335" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D335" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E335" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F335" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G335" s="18">
+        <f>SUM(C335:F335)</f>
+        <v/>
+      </c>
+      <c r="I335" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J335" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K335" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L335" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M335" s="18">
+        <f>SUM(I335:L335)</f>
+        <v/>
+      </c>
+      <c r="O335" s="19">
+        <f>IFERROR(I335/C335-1,"")</f>
+        <v/>
+      </c>
+      <c r="P335" s="19">
+        <f>IFERROR(J335/D335-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q335" s="19">
+        <f>IFERROR(K335/E335-1,"")</f>
+        <v/>
+      </c>
+      <c r="R335" s="19">
+        <f>IFERROR(L335/F335-1,"")</f>
+        <v/>
+      </c>
+      <c r="S335" s="19">
+        <f>IFERROR(M335/G335-1,"")</f>
+        <v/>
+      </c>
+      <c r="U335" s="20" t="n"/>
+      <c r="V335" s="20" t="n"/>
+      <c r="W335" s="20" t="n"/>
+      <c r="X335" s="20">
+        <f>IFERROR(W335-V335,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="336">
+      <c r="B336" s="12" t="inlineStr">
+        <is>
+          <t>PAYER</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="B337" s="13" t="inlineStr">
+        <is>
+          <t>0-9</t>
+        </is>
+      </c>
+      <c r="C337" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D337" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E337" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F337" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G337" s="14">
+        <f>SUM(C337:F337)</f>
+        <v/>
+      </c>
+      <c r="I337" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J337" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K337" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L337" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M337" s="14">
+        <f>SUM(I337:L337)</f>
+        <v/>
+      </c>
+      <c r="O337" s="15">
+        <f>IFERROR(I337/C337-1,"")</f>
+        <v/>
+      </c>
+      <c r="P337" s="15">
+        <f>IFERROR(J337/D337-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q337" s="15">
+        <f>IFERROR(K337/E337-1,"")</f>
+        <v/>
+      </c>
+      <c r="R337" s="15">
+        <f>IFERROR(L337/F337-1,"")</f>
+        <v/>
+      </c>
+      <c r="S337" s="15">
+        <f>IFERROR(M337/G337-1,"")</f>
+        <v/>
+      </c>
+      <c r="U337" s="16" t="n"/>
+      <c r="V337" s="16" t="n"/>
+      <c r="W337" s="16" t="n"/>
+      <c r="X337" s="16">
+        <f>IFERROR(W337-V337,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="338">
+      <c r="B338" s="13" t="inlineStr">
+        <is>
+          <t>10-19</t>
+        </is>
+      </c>
+      <c r="C338" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D338" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E338" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F338" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G338" s="14">
+        <f>SUM(C338:F338)</f>
+        <v/>
+      </c>
+      <c r="I338" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J338" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K338" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L338" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M338" s="14">
+        <f>SUM(I338:L338)</f>
+        <v/>
+      </c>
+      <c r="O338" s="15">
+        <f>IFERROR(I338/C338-1,"")</f>
+        <v/>
+      </c>
+      <c r="P338" s="15">
+        <f>IFERROR(J338/D338-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q338" s="15">
+        <f>IFERROR(K338/E338-1,"")</f>
+        <v/>
+      </c>
+      <c r="R338" s="15">
+        <f>IFERROR(L338/F338-1,"")</f>
+        <v/>
+      </c>
+      <c r="S338" s="15">
+        <f>IFERROR(M338/G338-1,"")</f>
+        <v/>
+      </c>
+      <c r="U338" s="16" t="n"/>
+      <c r="V338" s="16" t="n"/>
+      <c r="W338" s="16" t="n"/>
+      <c r="X338" s="16">
+        <f>IFERROR(W338-V338,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="339">
+      <c r="B339" s="13" t="inlineStr">
+        <is>
+          <t>20-39</t>
+        </is>
+      </c>
+      <c r="C339" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D339" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E339" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F339" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G339" s="14">
+        <f>SUM(C339:F339)</f>
+        <v/>
+      </c>
+      <c r="I339" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J339" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K339" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L339" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M339" s="14">
+        <f>SUM(I339:L339)</f>
+        <v/>
+      </c>
+      <c r="O339" s="15">
+        <f>IFERROR(I339/C339-1,"")</f>
+        <v/>
+      </c>
+      <c r="P339" s="15">
+        <f>IFERROR(J339/D339-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q339" s="15">
+        <f>IFERROR(K339/E339-1,"")</f>
+        <v/>
+      </c>
+      <c r="R339" s="15">
+        <f>IFERROR(L339/F339-1,"")</f>
+        <v/>
+      </c>
+      <c r="S339" s="15">
+        <f>IFERROR(M339/G339-1,"")</f>
+        <v/>
+      </c>
+      <c r="U339" s="16" t="n"/>
+      <c r="V339" s="16" t="n"/>
+      <c r="W339" s="16" t="n"/>
+      <c r="X339" s="16">
+        <f>IFERROR(W339-V339,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="340">
+      <c r="B340" s="13" t="inlineStr">
+        <is>
+          <t>40-99</t>
+        </is>
+      </c>
+      <c r="C340" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D340" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E340" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F340" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G340" s="14">
+        <f>SUM(C340:F340)</f>
+        <v/>
+      </c>
+      <c r="I340" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J340" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K340" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L340" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M340" s="14">
+        <f>SUM(I340:L340)</f>
+        <v/>
+      </c>
+      <c r="O340" s="15">
+        <f>IFERROR(I340/C340-1,"")</f>
+        <v/>
+      </c>
+      <c r="P340" s="15">
+        <f>IFERROR(J340/D340-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q340" s="15">
+        <f>IFERROR(K340/E340-1,"")</f>
+        <v/>
+      </c>
+      <c r="R340" s="15">
+        <f>IFERROR(L340/F340-1,"")</f>
+        <v/>
+      </c>
+      <c r="S340" s="15">
+        <f>IFERROR(M340/G340-1,"")</f>
+        <v/>
+      </c>
+      <c r="U340" s="16" t="n"/>
+      <c r="V340" s="16" t="n"/>
+      <c r="W340" s="16" t="n"/>
+      <c r="X340" s="16">
+        <f>IFERROR(W340-V340,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="341">
+      <c r="B341" s="13" t="inlineStr">
+        <is>
+          <t>100+</t>
+        </is>
+      </c>
+      <c r="C341" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D341" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E341" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F341" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G341" s="14">
+        <f>SUM(C341:F341)</f>
+        <v/>
+      </c>
+      <c r="I341" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J341" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K341" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L341" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M341" s="14">
+        <f>SUM(I341:L341)</f>
+        <v/>
+      </c>
+      <c r="O341" s="15">
+        <f>IFERROR(I341/C341-1,"")</f>
+        <v/>
+      </c>
+      <c r="P341" s="15">
+        <f>IFERROR(J341/D341-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q341" s="15">
+        <f>IFERROR(K341/E341-1,"")</f>
+        <v/>
+      </c>
+      <c r="R341" s="15">
+        <f>IFERROR(L341/F341-1,"")</f>
+        <v/>
+      </c>
+      <c r="S341" s="15">
+        <f>IFERROR(M341/G341-1,"")</f>
+        <v/>
+      </c>
+      <c r="U341" s="16" t="n"/>
+      <c r="V341" s="16" t="n"/>
+      <c r="W341" s="16" t="n"/>
+      <c r="X341" s="16">
+        <f>IFERROR(W341-V341,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="342">
+      <c r="B342" s="17" t="inlineStr">
+        <is>
+          <t>overall</t>
+        </is>
+      </c>
+      <c r="C342" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D342" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E342" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F342" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G342" s="18">
+        <f>SUM(C342:F342)</f>
+        <v/>
+      </c>
+      <c r="I342" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J342" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K342" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L342" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M342" s="18">
+        <f>SUM(I342:L342)</f>
+        <v/>
+      </c>
+      <c r="O342" s="19">
+        <f>IFERROR(I342/C342-1,"")</f>
+        <v/>
+      </c>
+      <c r="P342" s="19">
+        <f>IFERROR(J342/D342-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q342" s="19">
+        <f>IFERROR(K342/E342-1,"")</f>
+        <v/>
+      </c>
+      <c r="R342" s="19">
+        <f>IFERROR(L342/F342-1,"")</f>
+        <v/>
+      </c>
+      <c r="S342" s="19">
+        <f>IFERROR(M342/G342-1,"")</f>
+        <v/>
+      </c>
+      <c r="U342" s="20" t="n"/>
+      <c r="V342" s="20" t="n"/>
+      <c r="W342" s="20" t="n"/>
+      <c r="X342" s="20">
+        <f>IFERROR(W342-V342,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="345">
+      <c r="B345" s="2" t="inlineStr">
+        <is>
+          <t>◆ 6-star Pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="C346" s="3" t="inlineStr">
+        <is>
+          <t>◄ CURRENT (actuals: data + calc) ►</t>
+        </is>
+      </c>
+      <c r="D346" s="3" t="n"/>
+      <c r="E346" s="3" t="n"/>
+      <c r="F346" s="3" t="n"/>
+      <c r="G346" s="3" t="n"/>
+      <c r="I346" s="4" t="inlineStr">
+        <is>
+          <t>◄ SIMULATED (EcoGainsSim v4) ►</t>
+        </is>
+      </c>
+      <c r="J346" s="4" t="n"/>
+      <c r="K346" s="4" t="n"/>
+      <c r="L346" s="4" t="n"/>
+      <c r="M346" s="4" t="n"/>
+      <c r="O346" s="5" t="inlineStr">
+        <is>
+          <t>Δ</t>
+        </is>
+      </c>
+      <c r="P346" s="5" t="n"/>
+      <c r="Q346" s="5" t="n"/>
+      <c r="R346" s="5" t="n"/>
+      <c r="S346" s="5" t="n"/>
+      <c r="U346" s="6" t="inlineStr">
+        <is>
+          <t>◄ NET / earner (spend held constant) ►</t>
+        </is>
+      </c>
+      <c r="V346" s="6" t="n"/>
+      <c r="W346" s="6" t="n"/>
+      <c r="X346" s="6" t="n"/>
+    </row>
+    <row r="347">
+      <c r="B347" s="7" t="inlineStr">
+        <is>
+          <t>Segment</t>
+        </is>
+      </c>
+      <c r="C347" s="8" t="inlineStr">
+        <is>
+          <t>PAID</t>
+        </is>
+      </c>
+      <c r="D347" s="8" t="inlineStr">
+        <is>
+          <t>ADS</t>
+        </is>
+      </c>
+      <c r="E347" s="8" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="F347" s="8" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="G347" s="8" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="I347" s="9" t="inlineStr">
+        <is>
+          <t>PAID</t>
+        </is>
+      </c>
+      <c r="J347" s="9" t="inlineStr">
+        <is>
+          <t>ADS</t>
+        </is>
+      </c>
+      <c r="K347" s="9" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="L347" s="9" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="M347" s="9" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="O347" s="10" t="inlineStr">
+        <is>
+          <t>PAID</t>
+        </is>
+      </c>
+      <c r="P347" s="10" t="inlineStr">
+        <is>
+          <t>ADS</t>
+        </is>
+      </c>
+      <c r="Q347" s="10" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="R347" s="10" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="S347" s="10" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="U347" s="11" t="inlineStr">
+        <is>
+          <t>cur spend</t>
+        </is>
+      </c>
+      <c r="V347" s="11" t="inlineStr">
+        <is>
+          <t>cur net</t>
+        </is>
+      </c>
+      <c r="W347" s="11" t="inlineStr">
+        <is>
+          <t>new net</t>
+        </is>
+      </c>
+      <c r="X347" s="11" t="inlineStr">
+        <is>
+          <t>net Δ</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="B348" s="12" t="inlineStr">
+        <is>
+          <t>NONPAYER</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="B349" s="13" t="inlineStr">
+        <is>
+          <t>0-9</t>
+        </is>
+      </c>
+      <c r="C349" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D349" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E349" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F349" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G349" s="14">
+        <f>SUM(C349:F349)</f>
+        <v/>
+      </c>
+      <c r="I349" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J349" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K349" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L349" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M349" s="14">
+        <f>SUM(I349:L349)</f>
+        <v/>
+      </c>
+      <c r="O349" s="15">
+        <f>IFERROR(I349/C349-1,"")</f>
+        <v/>
+      </c>
+      <c r="P349" s="15">
+        <f>IFERROR(J349/D349-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q349" s="15">
+        <f>IFERROR(K349/E349-1,"")</f>
+        <v/>
+      </c>
+      <c r="R349" s="15">
+        <f>IFERROR(L349/F349-1,"")</f>
+        <v/>
+      </c>
+      <c r="S349" s="15">
+        <f>IFERROR(M349/G349-1,"")</f>
+        <v/>
+      </c>
+      <c r="U349" s="16" t="n"/>
+      <c r="V349" s="16" t="n"/>
+      <c r="W349" s="16" t="n"/>
+      <c r="X349" s="16">
+        <f>IFERROR(W349-V349,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="350">
+      <c r="B350" s="13" t="inlineStr">
+        <is>
+          <t>10-19</t>
+        </is>
+      </c>
+      <c r="C350" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D350" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E350" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F350" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G350" s="14">
+        <f>SUM(C350:F350)</f>
+        <v/>
+      </c>
+      <c r="I350" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J350" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K350" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L350" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M350" s="14">
+        <f>SUM(I350:L350)</f>
+        <v/>
+      </c>
+      <c r="O350" s="15">
+        <f>IFERROR(I350/C350-1,"")</f>
+        <v/>
+      </c>
+      <c r="P350" s="15">
+        <f>IFERROR(J350/D350-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q350" s="15">
+        <f>IFERROR(K350/E350-1,"")</f>
+        <v/>
+      </c>
+      <c r="R350" s="15">
+        <f>IFERROR(L350/F350-1,"")</f>
+        <v/>
+      </c>
+      <c r="S350" s="15">
+        <f>IFERROR(M350/G350-1,"")</f>
+        <v/>
+      </c>
+      <c r="U350" s="16" t="n"/>
+      <c r="V350" s="16" t="n"/>
+      <c r="W350" s="16" t="n"/>
+      <c r="X350" s="16">
+        <f>IFERROR(W350-V350,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="351">
+      <c r="B351" s="13" t="inlineStr">
+        <is>
+          <t>20-39</t>
+        </is>
+      </c>
+      <c r="C351" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D351" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E351" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F351" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G351" s="14">
+        <f>SUM(C351:F351)</f>
+        <v/>
+      </c>
+      <c r="I351" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J351" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K351" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L351" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M351" s="14">
+        <f>SUM(I351:L351)</f>
+        <v/>
+      </c>
+      <c r="O351" s="15">
+        <f>IFERROR(I351/C351-1,"")</f>
+        <v/>
+      </c>
+      <c r="P351" s="15">
+        <f>IFERROR(J351/D351-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q351" s="15">
+        <f>IFERROR(K351/E351-1,"")</f>
+        <v/>
+      </c>
+      <c r="R351" s="15">
+        <f>IFERROR(L351/F351-1,"")</f>
+        <v/>
+      </c>
+      <c r="S351" s="15">
+        <f>IFERROR(M351/G351-1,"")</f>
+        <v/>
+      </c>
+      <c r="U351" s="16" t="n"/>
+      <c r="V351" s="16" t="n"/>
+      <c r="W351" s="16" t="n"/>
+      <c r="X351" s="16">
+        <f>IFERROR(W351-V351,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="352">
+      <c r="B352" s="13" t="inlineStr">
+        <is>
+          <t>40-99</t>
+        </is>
+      </c>
+      <c r="C352" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D352" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E352" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F352" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G352" s="14">
+        <f>SUM(C352:F352)</f>
+        <v/>
+      </c>
+      <c r="I352" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J352" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K352" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L352" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M352" s="14">
+        <f>SUM(I352:L352)</f>
+        <v/>
+      </c>
+      <c r="O352" s="15">
+        <f>IFERROR(I352/C352-1,"")</f>
+        <v/>
+      </c>
+      <c r="P352" s="15">
+        <f>IFERROR(J352/D352-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q352" s="15">
+        <f>IFERROR(K352/E352-1,"")</f>
+        <v/>
+      </c>
+      <c r="R352" s="15">
+        <f>IFERROR(L352/F352-1,"")</f>
+        <v/>
+      </c>
+      <c r="S352" s="15">
+        <f>IFERROR(M352/G352-1,"")</f>
+        <v/>
+      </c>
+      <c r="U352" s="16" t="n"/>
+      <c r="V352" s="16" t="n"/>
+      <c r="W352" s="16" t="n"/>
+      <c r="X352" s="16">
+        <f>IFERROR(W352-V352,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="353">
+      <c r="B353" s="13" t="inlineStr">
+        <is>
+          <t>100+</t>
+        </is>
+      </c>
+      <c r="C353" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D353" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E353" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F353" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G353" s="14">
+        <f>SUM(C353:F353)</f>
+        <v/>
+      </c>
+      <c r="I353" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J353" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K353" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L353" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M353" s="14">
+        <f>SUM(I353:L353)</f>
+        <v/>
+      </c>
+      <c r="O353" s="15">
+        <f>IFERROR(I353/C353-1,"")</f>
+        <v/>
+      </c>
+      <c r="P353" s="15">
+        <f>IFERROR(J353/D353-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q353" s="15">
+        <f>IFERROR(K353/E353-1,"")</f>
+        <v/>
+      </c>
+      <c r="R353" s="15">
+        <f>IFERROR(L353/F353-1,"")</f>
+        <v/>
+      </c>
+      <c r="S353" s="15">
+        <f>IFERROR(M353/G353-1,"")</f>
+        <v/>
+      </c>
+      <c r="U353" s="16" t="n"/>
+      <c r="V353" s="16" t="n"/>
+      <c r="W353" s="16" t="n"/>
+      <c r="X353" s="16">
+        <f>IFERROR(W353-V353,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="354">
+      <c r="B354" s="17" t="inlineStr">
+        <is>
+          <t>overall</t>
+        </is>
+      </c>
+      <c r="C354" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D354" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E354" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F354" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G354" s="18">
+        <f>SUM(C354:F354)</f>
+        <v/>
+      </c>
+      <c r="I354" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J354" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K354" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L354" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M354" s="18">
+        <f>SUM(I354:L354)</f>
+        <v/>
+      </c>
+      <c r="O354" s="19">
+        <f>IFERROR(I354/C354-1,"")</f>
+        <v/>
+      </c>
+      <c r="P354" s="19">
+        <f>IFERROR(J354/D354-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q354" s="19">
+        <f>IFERROR(K354/E354-1,"")</f>
+        <v/>
+      </c>
+      <c r="R354" s="19">
+        <f>IFERROR(L354/F354-1,"")</f>
+        <v/>
+      </c>
+      <c r="S354" s="19">
+        <f>IFERROR(M354/G354-1,"")</f>
+        <v/>
+      </c>
+      <c r="U354" s="20" t="n"/>
+      <c r="V354" s="20" t="n"/>
+      <c r="W354" s="20" t="n"/>
+      <c r="X354" s="20">
+        <f>IFERROR(W354-V354,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="355">
+      <c r="B355" s="12" t="inlineStr">
+        <is>
+          <t>PAYER</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="B356" s="13" t="inlineStr">
+        <is>
+          <t>0-9</t>
+        </is>
+      </c>
+      <c r="C356" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D356" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E356" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F356" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G356" s="14">
+        <f>SUM(C356:F356)</f>
+        <v/>
+      </c>
+      <c r="I356" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J356" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K356" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L356" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M356" s="14">
+        <f>SUM(I356:L356)</f>
+        <v/>
+      </c>
+      <c r="O356" s="15">
+        <f>IFERROR(I356/C356-1,"")</f>
+        <v/>
+      </c>
+      <c r="P356" s="15">
+        <f>IFERROR(J356/D356-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q356" s="15">
+        <f>IFERROR(K356/E356-1,"")</f>
+        <v/>
+      </c>
+      <c r="R356" s="15">
+        <f>IFERROR(L356/F356-1,"")</f>
+        <v/>
+      </c>
+      <c r="S356" s="15">
+        <f>IFERROR(M356/G356-1,"")</f>
+        <v/>
+      </c>
+      <c r="U356" s="16" t="n"/>
+      <c r="V356" s="16" t="n"/>
+      <c r="W356" s="16" t="n"/>
+      <c r="X356" s="16">
+        <f>IFERROR(W356-V356,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="357">
+      <c r="B357" s="13" t="inlineStr">
+        <is>
+          <t>10-19</t>
+        </is>
+      </c>
+      <c r="C357" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D357" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E357" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F357" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G357" s="14">
+        <f>SUM(C357:F357)</f>
+        <v/>
+      </c>
+      <c r="I357" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J357" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K357" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L357" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M357" s="14">
+        <f>SUM(I357:L357)</f>
+        <v/>
+      </c>
+      <c r="O357" s="15">
+        <f>IFERROR(I357/C357-1,"")</f>
+        <v/>
+      </c>
+      <c r="P357" s="15">
+        <f>IFERROR(J357/D357-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q357" s="15">
+        <f>IFERROR(K357/E357-1,"")</f>
+        <v/>
+      </c>
+      <c r="R357" s="15">
+        <f>IFERROR(L357/F357-1,"")</f>
+        <v/>
+      </c>
+      <c r="S357" s="15">
+        <f>IFERROR(M357/G357-1,"")</f>
+        <v/>
+      </c>
+      <c r="U357" s="16" t="n"/>
+      <c r="V357" s="16" t="n"/>
+      <c r="W357" s="16" t="n"/>
+      <c r="X357" s="16">
+        <f>IFERROR(W357-V357,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="358">
+      <c r="B358" s="13" t="inlineStr">
+        <is>
+          <t>20-39</t>
+        </is>
+      </c>
+      <c r="C358" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D358" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E358" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F358" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G358" s="14">
+        <f>SUM(C358:F358)</f>
+        <v/>
+      </c>
+      <c r="I358" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J358" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K358" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L358" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M358" s="14">
+        <f>SUM(I358:L358)</f>
+        <v/>
+      </c>
+      <c r="O358" s="15">
+        <f>IFERROR(I358/C358-1,"")</f>
+        <v/>
+      </c>
+      <c r="P358" s="15">
+        <f>IFERROR(J358/D358-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q358" s="15">
+        <f>IFERROR(K358/E358-1,"")</f>
+        <v/>
+      </c>
+      <c r="R358" s="15">
+        <f>IFERROR(L358/F358-1,"")</f>
+        <v/>
+      </c>
+      <c r="S358" s="15">
+        <f>IFERROR(M358/G358-1,"")</f>
+        <v/>
+      </c>
+      <c r="U358" s="16" t="n"/>
+      <c r="V358" s="16" t="n"/>
+      <c r="W358" s="16" t="n"/>
+      <c r="X358" s="16">
+        <f>IFERROR(W358-V358,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="359">
+      <c r="B359" s="13" t="inlineStr">
+        <is>
+          <t>40-99</t>
+        </is>
+      </c>
+      <c r="C359" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D359" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E359" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F359" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G359" s="14">
+        <f>SUM(C359:F359)</f>
+        <v/>
+      </c>
+      <c r="I359" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J359" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K359" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L359" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M359" s="14">
+        <f>SUM(I359:L359)</f>
+        <v/>
+      </c>
+      <c r="O359" s="15">
+        <f>IFERROR(I359/C359-1,"")</f>
+        <v/>
+      </c>
+      <c r="P359" s="15">
+        <f>IFERROR(J359/D359-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q359" s="15">
+        <f>IFERROR(K359/E359-1,"")</f>
+        <v/>
+      </c>
+      <c r="R359" s="15">
+        <f>IFERROR(L359/F359-1,"")</f>
+        <v/>
+      </c>
+      <c r="S359" s="15">
+        <f>IFERROR(M359/G359-1,"")</f>
+        <v/>
+      </c>
+      <c r="U359" s="16" t="n"/>
+      <c r="V359" s="16" t="n"/>
+      <c r="W359" s="16" t="n"/>
+      <c r="X359" s="16">
+        <f>IFERROR(W359-V359,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="360">
+      <c r="B360" s="13" t="inlineStr">
+        <is>
+          <t>100+</t>
+        </is>
+      </c>
+      <c r="C360" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D360" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E360" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F360" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G360" s="14">
+        <f>SUM(C360:F360)</f>
+        <v/>
+      </c>
+      <c r="I360" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J360" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K360" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L360" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M360" s="14">
+        <f>SUM(I360:L360)</f>
+        <v/>
+      </c>
+      <c r="O360" s="15">
+        <f>IFERROR(I360/C360-1,"")</f>
+        <v/>
+      </c>
+      <c r="P360" s="15">
+        <f>IFERROR(J360/D360-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q360" s="15">
+        <f>IFERROR(K360/E360-1,"")</f>
+        <v/>
+      </c>
+      <c r="R360" s="15">
+        <f>IFERROR(L360/F360-1,"")</f>
+        <v/>
+      </c>
+      <c r="S360" s="15">
+        <f>IFERROR(M360/G360-1,"")</f>
+        <v/>
+      </c>
+      <c r="U360" s="16" t="n"/>
+      <c r="V360" s="16" t="n"/>
+      <c r="W360" s="16" t="n"/>
+      <c r="X360" s="16">
+        <f>IFERROR(W360-V360,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="361">
+      <c r="B361" s="17" t="inlineStr">
+        <is>
+          <t>overall</t>
+        </is>
+      </c>
+      <c r="C361" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D361" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E361" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F361" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G361" s="18">
+        <f>SUM(C361:F361)</f>
+        <v/>
+      </c>
+      <c r="I361" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J361" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K361" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L361" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M361" s="18">
+        <f>SUM(I361:L361)</f>
+        <v/>
+      </c>
+      <c r="O361" s="19">
+        <f>IFERROR(I361/C361-1,"")</f>
+        <v/>
+      </c>
+      <c r="P361" s="19">
+        <f>IFERROR(J361/D361-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q361" s="19">
+        <f>IFERROR(K361/E361-1,"")</f>
+        <v/>
+      </c>
+      <c r="R361" s="19">
+        <f>IFERROR(L361/F361-1,"")</f>
+        <v/>
+      </c>
+      <c r="S361" s="19">
+        <f>IFERROR(M361/G361-1,"")</f>
+        <v/>
+      </c>
+      <c r="U361" s="20" t="n"/>
+      <c r="V361" s="20" t="n"/>
+      <c r="W361" s="20" t="n"/>
+      <c r="X361" s="20">
+        <f>IFERROR(W361-V361,"")</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
